--- a/资料/数据集.xlsx
+++ b/资料/数据集.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E2007"/>
+  <dimension ref="B2:E2008"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="2.73" customWidth="1" style="9" min="1" max="1"/>
@@ -940,7 +940,11 @@
           <t>第1步：取1000g小龙虾放入大号双耳盘中，加入200g香辣小龙虾调料、1根黄瓜（去芯切条）和2个青椒（切片），再倒入200g啤酒混合均匀备用。；第2步：取500g小龙虾放入中号碗中，加入100g油焖小龙虾调料、半根黄瓜（去芯切条）和1个青椒（切片），再倒入200g啤酒混合均匀备用。；第3步：取500g小龙虾放入中号碗中，加入150g蒜香小龙虾调料、半根黄瓜（去芯切条）和1个青椒（切片），混合均匀备用。；第4步：将泡软的龙口粉丝和金针菇铺在小号碗中，均匀放入100g蒜蓉酱备用。；第5步：将毛豆放入小号碗中，加入4g盐和400g开水混合均匀备用。；第6步：将三盘小龙虾置于蒸烤盘上放入机器上层，粉丝金针菇和毛豆置于蒸烤架上放入下层。；第7步：取出水箱加满水，在设备/APP端找到并进入“小龙虾套餐”，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E23" s="14" t="n"/>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>晚餐、川湘菜、辣、香辣、鲜美、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="48" customHeight="1" s="10">
       <c r="B24" s="15" t="inlineStr">
@@ -1134,7 +1138,11 @@
           <t>第1步：土豆清洗干净，削去外皮；第2步：将土豆切成块；第3步：放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第4步：将切好的鳕鱼清洗干净，放入小煮锅中，加入适量冷水（水量以没过鱼肉1cm即可），大火煮熟，捞出；第5步：将蒸熟的土豆和煮熟的鱼肉放入碗中，用勺背均匀地压碎成泥；第6步：取2茶匙（10毫升）煮鳕鱼的鱼汤倒入土豆、鳕鱼泥中，加入盐，用勺子轻轻地搅拌均匀成黏稠状；第7步：健康又美味</t>
         </is>
       </c>
-      <c r="E32" s="16" t="n"/>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>早餐、午餐、儿童、老人、养胃、健胃消食</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="48" customHeight="1" s="10">
       <c r="B33" s="13" t="inlineStr">
@@ -1196,7 +1204,11 @@
           <t>第1步：食材准备；第2步：枸杞泡发洗净吸干水分待用；第3步：将核桃切碎块；第4步：去枣核切片；第5步：将冰糖粉、阿胶粉、黄酒混合，搅拌均匀；第6步：加入其它配料，拌匀。装入深盘中，用保鲜膜封口；第7步：放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第8步：取出后冷却切块，即可食用</t>
         </is>
       </c>
-      <c r="E35" s="14" t="n"/>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、中式面点、甜、更年期、老人、哺乳、贫血、助眠</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="48" customHeight="1" s="10">
       <c r="B36" s="15" t="inlineStr">
@@ -1236,7 +1248,11 @@
           <t>第1步：把红枣洗净后，剪成条，备用。；第2步：红枣里加上糯米粉，面粉，糖，和分次少量加入牛奶揉成面团，再整形成长条型面团。；第3步：把面团切成小段，放入盘里。；第4步：打开方太智能烹饪设备，将蒸烤架放入蒸箱第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E37" s="14" t="n"/>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>早餐、下午茶、中式面点、甜、儿童、老人、助眠</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="48" customHeight="1" s="10">
       <c r="B38" s="15" t="inlineStr">
@@ -1496,7 +1512,11 @@
           <t>第1步：在碗里打入2个鸡蛋，加入糖，和牛奶搅拌均匀；第2步：加入融化的黄油，继续搅拌。；第3步：倒入糯米粉，搅拌均匀。；第4步：将面糊过筛。；第5步：模具刷油。；第6步：倒入过筛后的面糊，八分满。；第7步：打开蒸烤一体机，将烤架放在蒸烤一体机第 2层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E49" s="14" t="n"/>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、中式面点、甜、甜点</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="48" customHeight="1" s="10">
       <c r="B50" s="15" t="inlineStr">
@@ -1646,7 +1666,11 @@
           <t>第1步：提前1小时，取1小碗放入干贝，加入冷水浸泡。；第2步：将虾剥壳、去虾线。；第3步：虾仁用刀背剁碎，剁出胶质。；第4步：将虾泥放入盆里，加上蛋清、葱姜水和盐搅拌均匀，搅到黏稠后再加入8克淀粉搅打上劲。；第5步：将虾滑装入裱花袋备用。；第6步：将丝瓜去皮切成约2.5厘米的段，用挖球器挖出瓜瓤，在盘里摆整齐。；第7步：裱花袋剪个小口，将虾滑挤入丝瓜洞中。；第8步：泡发好的干贝撕成小条放入碗里，加入2克淀粉、白胡椒粉、生抽和清水搅拌均匀。；第9步：将调好的芡汁均匀的淋在虾滑上。；第10步：将装有丝瓜酿虾滑的盘子放在蒸烤架上。开启电源，取出水箱加满水，将蒸烤架放入烹饪机中间层，选择【开始烹饪】按键，按屏幕提示操作即可。</t>
         </is>
       </c>
-      <c r="E56" s="16" t="n"/>
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、粤菜、江浙菜、清淡、鲜美、儿童、老人、养胃、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="48" customHeight="1" s="10">
       <c r="B57" s="13" t="inlineStr">
@@ -1688,7 +1712,7 @@
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、川湘菜、辣、香辣、咸、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1908,11 @@
           <t>第1步：油麦菜洗净，切成7-8cm大小的段；第2步：将蒜末和盐1g，白糖2g，鸡精0.5g，生抽5g，蚝油2g放入碗中拌匀，备用；第3步：中号盘中加入猪油10g和玉米油10g，放在蒸烤架上，放入机器第二层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。；第4步：将蒜末调味汁加入到油麦菜中，翻拌均匀备用；第5步：热油结束，将油麦菜放入中号盘中，翻拌均匀，关门继续烹饪。</t>
         </is>
       </c>
-      <c r="E67" s="14" t="n"/>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、川湘菜、江浙菜、清淡、咸、蒜香、上班族、减脂、便秘、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="48" customHeight="1" s="10">
       <c r="B68" s="15" t="inlineStr">
@@ -1968,7 +1996,11 @@
           <t>第1步：将温开水分次缓慢加入到粉中，每加一点水便用双手搓揉粉，使其形成砂砾状态。当粉末可以捏成团状并能轻松碎掉即可停止加水。取一个大号筛网，将米粉团过筛成细腻粉状备用。；第2步：准备好专用米糕模具，四周刷上少量食用油，将米粉倒入，表面抹平，再倒扣在垫有有空硅胶垫上的蒸烤架上，做成独立糕体。；第3步：打开蒸烤箱，将模具置于蒸烤架上并放入第二层，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E71" s="14" t="n"/>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>早餐、下午茶、中式面点、甜、儿童、老人、养胃、健胃消食</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="48" customHeight="1" s="10">
       <c r="B72" s="15" t="inlineStr">
@@ -2008,7 +2040,11 @@
           <t>第1步：洗净的荠菜对半切开，码放在盘中备用。；第2步：火腿切片，铺在芥菜上。；第3步：打开蒸烤一体机，将蒸烤架放在蒸烤一体机第 2层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。；第4步：取出淋上蒸鱼豉油。</t>
         </is>
       </c>
-      <c r="E73" s="14" t="n"/>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、粤菜、清淡、咸、老人、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="48" customHeight="1" s="10">
       <c r="B74" s="15" t="inlineStr">
@@ -2050,7 +2086,7 @@
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>午餐、晚餐、西餐风味、清淡、鲜美、减脂、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2216,11 @@
           <t>第1步：竹笋洗净，切滚刀块。；第2步：放入盘中后，撒上盐1g、鸡粉2g抓匀备用。；第3步：大虾放入碗中加入0.5g盐、0.5g鸡粉备用。；第4步：大虾干放在竹笋上，放上剁椒20g。；第5步：打开蒸烤一体机，将蒸烤架放在蒸烤一体机第 2层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。；第6步：取出撒上葱花，淋上热油。</t>
         </is>
       </c>
-      <c r="E81" s="14" t="n"/>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、清淡、鲜美、老人、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="48" customHeight="1" s="10">
       <c r="B82" s="15" t="inlineStr">
@@ -2220,7 +2260,11 @@
           <t>第1步：将橘皮、茯苓、菊苣和葛根，加纯净水浸泡10分钟。；第2步：将橘皮茶放在蒸烤架上，放入机器中间层，设置普通蒸100℃，30分钟。</t>
         </is>
       </c>
-      <c r="E83" s="14" t="n"/>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、更年期、老人、养胃、健胃消食</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="48" customHeight="1" s="10">
       <c r="B84" s="15" t="inlineStr">
@@ -2238,7 +2282,11 @@
           <t>第1步：法式烤布蕾：将200g淡奶油和180g牛奶混合均匀，在锅中加热至冒小泡后关火放凉。；第2步：将30g细砂糖加入6个蛋黄中搅拌均匀。将放凉的奶液倒入蛋液中，搅拌均匀，过筛，倒入小号碗中。；第3步：迷你布朗尼：将140g黄油和100g巧克力切小块，放入料理盆中隔水加热融化，水温约60℃。；第4步：在融化的黄油和巧克力中加入120g糖粉，用手动打蛋器搅拌均匀。将2个鸡蛋打散成蛋液，分3次加入搅拌均匀。；第5步：加入60g过筛的低筋面粉、2g泡打粉和40g熟核桃碎，用刮刀翻拌均匀。将面糊装入裱花袋中，挤入纸杯约5- 6分满，放入大号双耳盘备用。；第6步：芒果雪媚娘：将100g糯米粉、30g玉米淀粉、50g白砂糖、170g牛奶混合均匀成无颗粒的粉浆。；第7步：将粉浆过筛，倒进中号碗中，盖上保鲜膜，戳两个小洞，备用。；第8步：桃胶牛奶羹：20g桃胶、3g雪燕、15g皂角米分别装入碗中，加入清水提前一晚泡发。；第9步：浸泡好后的桃胶、雪燕和皂角米挑去杂质，清洗干净。将桃胶、雪燕和皂角米放入小号碗中，加入400g牛奶、20g冰糖和5g枸杞，备用。；第10步：缤纷水果茶：将半个橙子、半个苹果、半个香梨洗净切片。在中号碗中加入水果片、适量冰糖和500g纯净水，备用。；第11步：将法式烤布蕾、迷你布朗尼置于蒸烤盘上放入机器上层，雪媚娘、桃胶牛奶羹、缤纷水果茶置于蒸烤架上放入下层。取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E84" s="16" t="n"/>
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、西餐风味、甜、甜点、儿童、上班族、更年期、老人</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="48" customHeight="1" s="10">
       <c r="B85" s="13" t="inlineStr">
@@ -2872,7 +2920,11 @@
           <t>第1步：主锅中加入橄榄油和小干葱碎，盖上锅盖，设置：3分钟/热炒/中火。；第2步：加入白蘑菇丁，盖上锅盖，设置：5分钟/热炒/中火。结束后，倒出备用并清洗主锅。；第3步：主锅中加入意大利米，盖上锅盖，设置：3分钟/热炒/小火；再加入葡萄酒小火炒1分钟。；第4步：主锅中加入热鸡汤、炒好的蘑菇丁、菠菜叶、盐和黑胡椒粉，盖上锅盖，设置：18分钟/烧煮/中火。；第5步：主锅中加入大蒜碎、意大利芹碎，盖上锅盖焖2分钟。；第6步：主锅中加入黄油和帕玛森芝士调味。；第7步：烹饪结束，取出倒入盘中，以蘑菇片、菠菜叶和芝士片稍加点缀即可享用。</t>
         </is>
       </c>
-      <c r="E113" s="14" t="n"/>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、西餐风味、奶香、咸、清淡、上班族、养胃</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="48" customHeight="1" s="10">
       <c r="B114" s="15" t="inlineStr">
@@ -3110,7 +3162,11 @@
           <t>第1步：将榴莲肉碾碎备用。；第2步：淡奶油加入12克白砂糖用打蛋器打发后，拌入150克碾碎的榴莲肉。；第3步：将榴莲馅料装入裱花袋。冰格铺上保鲜膜，将馅料挤入冰格，每个20克，放入冰箱冷冻至硬。；第4步：取1盆，放入糯米粉、粘米粉、澄面、牛奶和45克白砂糖，搅拌均匀，过筛网倒入大的平底盘中平铺一层。；第5步：将平底盘放在蒸烤架上。开启电源，将蒸烤架放入烹饪机下层，蒸烤盘放入烹饪机中间层，选择【开始烹饪】按键，按屏幕提示操作即可。；第6步：烹饪结束后取出食材，趁热在平底盘中加入黄油融化，待糕团凉至不烫手时，使用一次性手套，用手掌根压塌、搓揉，直到黄油完全与糕团混合均匀且表面光洁不粘手。；第7步：将冰皮糕团搓成长条，用刮刀分成约25克一个的剂子。；第8步：将冰皮剂子搓圆、擀平，捏成小碗状，包入冷冻好的榴莲馅心，裹成圆球状。；第9步：将圆球裹一层熟糯米粉，放入规格为30克的月饼模型中，按压成月饼形状。</t>
         </is>
       </c>
-      <c r="E124" s="16" t="n"/>
+      <c r="E124" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、中秋、甜、甜点、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="48" customHeight="1" s="10">
       <c r="B125" s="13" t="inlineStr">
@@ -3128,7 +3184,11 @@
           <t>第1步：将龙虾处理好，对半剖开。；第2步：将粉丝用开水泡软，切成小段，小葱切葱花备用。；第3步：油蒜末：将炒锅加热，放入B中食用油，加入蒜末，小火煸香，待蒜末呈淡黄色时盛出。；第4步：蒜蓉中加入D中酱汁混匀备用。；第5步：蒸龙虾准备：盘中铺一层泡软的粉丝，加少许水浸润粉丝，摆上龙虾，龙虾肉和粉丝上铺一层蒜蓉酱。将盘子放在蒸烤架上.；第6步：开启电源，取出水箱加满水，将蒸烤架烹饪机中间层，选择【开始烹饪】按键，按屏幕提示操作即可。</t>
         </is>
       </c>
-      <c r="E125" s="14" t="n"/>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、粤菜、海鲜风味、鲜美、蒜香、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="48" customHeight="1" s="10">
       <c r="B126" s="15" t="inlineStr">
@@ -3894,7 +3954,11 @@
           <t>第1步：肉切成大块，用水浸泡30分钟泡出血水，捞出擦干水分。；第2步：生姜大葱切末备用。；第3步：羊肉加入所有调味料拌匀，放入碗中，浇上热油。；第4步：打开蒸烤一体机，将烤架放在蒸烤一体机第2层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E160" s="16" t="n"/>
+      <c r="E160" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、川湘菜、咸、咸香、老人、养胃、贫血、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="48" customHeight="1" s="10">
       <c r="B161" s="13" t="inlineStr">
@@ -4264,7 +4328,11 @@
           <t>第1步：盐酥鸡无需解冻，铺在蒸烤架上；第2步：打开方太智能烹饪设备，将蒸烤机放入设备第2层，蒸烤盘放入第一层接汁，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E177" s="14" t="n"/>
+      <c r="E177" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、台式风味、咸、脆、香脆、儿童、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="48" customHeight="1" s="10">
       <c r="B178" s="15" t="inlineStr">
@@ -4282,7 +4350,11 @@
           <t>第1步：放置在铺有锡纸的蒸烤盘上。；第2步：打开蒸烤箱，将蒸烤盘放入第二层，按屏幕提示操作。；第3步：即可享用</t>
         </is>
       </c>
-      <c r="E178" s="16" t="n"/>
+      <c r="E178" s="16" t="inlineStr">
+        <is>
+          <t>早餐、西餐风味、咸、奶香、儿童、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="48" customHeight="1" s="10">
       <c r="B179" s="13" t="inlineStr">
@@ -4346,7 +4418,7 @@
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>下午茶、地方风味、甜、儿童、老人、烤制类</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4636,11 @@
           <t>第1步：料理盆中加入擦干的排骨段、豆豉末、葱白末、姜末、蒜末、陈皮丝、料酒、盐、蚝油、生抽，充分拌匀后腌制40分钟；再加入玉米淀粉，充分搅拌均匀放入盘中备用。；第2步：将豉汁排骨放在蒸烤架上，放入机器中间层，设置普通蒸100℃，45分钟。</t>
         </is>
       </c>
-      <c r="E191" s="14" t="n"/>
+      <c r="E191" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、粤菜、豉香、咸、清淡、老人、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="48" customHeight="1" s="10">
       <c r="B192" s="15" t="inlineStr">
@@ -4626,7 +4702,11 @@
           <t>第1步：把腊肠放入水中快速清洗，捞出斜切成片；将姜片切成姜丝；小葱切葱花。；第2步：将油菜心洗净，明火水开焯水30秒备用。；第3步：调味酱汁制作：将调料中除玉米油外的所有调味料倒入小碗中搅拌均匀即成调味酱汁。；第4步：称取五常大米150g，放入大碗中，倒入清水用手淘洗三次后沥出水。；第5步：取一砂锅洗净，用厨房纸巾擦干，往砂锅中倒入5g玉米油，用刷子涂抹砂锅壁，均匀的抹一层油脂。将砂锅放在电子称上去皮归零，把五常大米放入砂锅中加入清水，米水总重量315g(米水比为1：1.1)，放入腊肠片和姜丝，盖上砂锅盖子。；第6步：将砂锅放置在蒸烤架上，放在机器第一层，开启电源，取出水箱加满水，选择烹饪属性，按确认键开始烹饪。；第7步：烹饪时间剩余10分钟后，取出砂锅，打开盖子，锅边淋入剩余的5g玉米油，在米饭表面敲入一个鸡蛋，盖上盖子，继续烹饪。；第8步：烹饪结束，打开砂锅盖子，倒入调味酱汁，沿砂锅边缘摆入油菜心，撒上葱花，盖上盖子焖5分钟，拌均匀即可食用；第9步：烹饪结束后取出，拌匀即可食用。</t>
         </is>
       </c>
-      <c r="E194" s="16" t="n"/>
+      <c r="E194" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、粤菜、咸、香、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="48" customHeight="1" s="10">
       <c r="B195" s="13" t="inlineStr">
@@ -5084,7 +5164,11 @@
           <t>第1步：食材准备；第2步：20克生姜切丝，小葱洗净葱白切段，葱绿切长丝，小米椒切丝；第3步：鲈鱼处理干净，鱼身两面都竖割一刀，用厨房纸擦干表面；第4步：鲈鱼中加入20毫升料酒、2克白胡椒粉、2克食盐、5毫升香油、15毫升生抽，涂抹均匀；鱼肚中塞入葱白段、姜丝，放置腌制30分钟；第5步：鱼身两面都抹上黄豆酱；第6步：方太SCD39-C2.i智能蒸箱设置100℃，15分钟；第7步：放入蒸制；第8步：蒸好取出，淋上香油，点缀葱椒丝；享用黄豆酱蒸鱼吧</t>
         </is>
       </c>
-      <c r="E215" s="14" t="n"/>
+      <c r="E215" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、粤菜、江浙菜、酱香、咸、鲜美、清淡、老人、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="48" customHeight="1" s="10">
       <c r="B216" s="15" t="inlineStr">
@@ -5502,7 +5586,11 @@
           <t>第1步：食材准备；第2步：将酵母粉用温水化开，之后倒入面粉中搅拌均匀揉成光滑的面团；第3步：揉好后盖上保鲜膜，醒15分钟；第4步：之后将面团分成4等份，分别搓成长条；第5步：把长条摆成U形，拿一根切好的胡萝卜条,放在下面；第6步：把面缠绕过胡萝卜条；第7步：整形，把出头的面团捏成均匀的兔耳朵形状，用牙签按压一下；第8步：用筷子做几个凹点，作为兔子的眼睛和嘴巴，将蜜豆放在眼睛位置，做好后将小兔子放在一旁进行二次发酵；第9步：放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第10步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E234" s="16" t="n"/>
+      <c r="E234" s="16" t="inlineStr">
+        <is>
+          <t>早餐、中式面点、清淡、甜、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="48" customHeight="1" s="10">
       <c r="B235" s="13" t="inlineStr">
@@ -5542,7 +5630,11 @@
           <t>第1步：取出牛油果果肉捣碎，再加入黄芥末酱拌匀备用。；第2步：沿长边将鸡胸肉均匀切成三片，加入柠檬汁、海盐和黑胡椒碎腌制30分钟备用。；第3步：将鸡胸肉平铺在铺有油纸的烤盘上，鸡蛋打在三个不沾金属碗中。；第4步：将全麦吐司片包在锡纸里，平放在烤架上。；第5步：将烤盘放入第四层，烤架放入第一层，选择双温同烤，上-200℃，下150℃，10分钟，</t>
         </is>
       </c>
-      <c r="E236" s="16" t="n"/>
+      <c r="E236" s="16" t="inlineStr">
+        <is>
+          <t>早餐、西餐风味、清淡、减脂、上班族、便秘</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="48" customHeight="1" s="10">
       <c r="B237" s="13" t="inlineStr">
@@ -5582,7 +5674,11 @@
           <t>第1步：食材准备；第2步：分离蛋清：将鸡蛋打入碗中，把蛋黄取出不用；第3步：在蛋清中加入白糖用手持打蛋器打均匀；第4步：将纯牛奶倒入奶锅中，用小火煮至微沸状态；第5步：将牛奶倒进6-7个小碗里，放凉，表面会结成一层奶皮；第6步：将碗中牛奶沿碗的边缘倒进蛋清中，碗底留下奶皮；第7步：将蛋清和牛奶搅拌均匀，用网筛过滤气泡；第8步：把蛋清、牛奶混合物沿碗边缓缓倒进碗中，奶皮会自动浮起来；第9步：打开方太C2.i蒸箱，选择普通蒸模式，设置100℃；第10步：将小碗放入有孔蒸盘上，放入蒸箱中间层蒸制15分钟；第11步：烹饪结束后，取出蒸好的双皮奶，冷却，便会结成一层皮，加上蜜红豆即可；第12步：尽情享用美味的红豆双皮奶吧</t>
         </is>
       </c>
-      <c r="E238" s="16" t="n"/>
+      <c r="E238" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、粤菜、甜、甜品、儿童、老人、养胃</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="48" customHeight="1" s="10">
       <c r="B239" s="13" t="inlineStr">
@@ -5668,7 +5764,7 @@
       </c>
       <c r="E242" s="16" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、西餐风味、咸、上班族、贫血、烤制类</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5786,7 @@
       </c>
       <c r="E243" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、情人节、西餐风味、咸、上班族、更年期、烤制类</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5808,7 @@
       </c>
       <c r="E244" s="16" t="inlineStr">
         <is>
-          <t>耗时长、汤类</t>
+          <t>午餐、晚餐、川湘菜、清淡、鲜美、哺乳、养胃、贫血、耗时长、汤类、家常菜</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5850,11 @@
           <t>第1步：猪肉切片，清洗干净备用。；第2步：白萝卜切1mm的细丝备用。；第3步：猪肉片中加入盐、鸡精、胡椒粉、清水，腌拌入味，放入红薯粉、澄面拌匀。；第4步：烧一锅开水，将腌制好的肉片，一片片的放入水中烫煮定型。；第5步：盘中垫入白萝卜丝，放上汆烫好的肉片，撒上撕碎的紫菜。；第6步：打开蒸烤一体机，将蒸烤架放在蒸烤一体机第2层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E246" s="16" t="n"/>
+      <c r="E246" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、清淡、鲜美、儿童、老人、养胃、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="48" customHeight="1" s="10">
       <c r="B247" s="13" t="inlineStr">
@@ -6080,7 +6180,11 @@
           <t>第1步：猪肋排加入盐2g、生粉2g揉出杂质，清洗干净备用。；第2步：豆豉切碎备用。；第3步：把豆豉碎、蒜蓉、黑胡椒碎放入碗中，用热油爆香后备用。；第4步：把爆香过的豆豉蒜蓉酱、生抽、蚝油、糖、盐和生粉放入排骨中，搅拌均匀。；第5步：烤盘上铺上油纸，淋上鸡油，再放上排骨。；第6步：打开蒸烤一体机，将蒸烤架放在蒸烤一体机第 2层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。；第7步：取出撒上姜丝和葱花。</t>
         </is>
       </c>
-      <c r="E261" s="14" t="n"/>
+      <c r="E261" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、粤菜、豉香、咸、上班族、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="48" customHeight="1" s="10">
       <c r="B262" s="15" t="inlineStr">
@@ -6143,7 +6247,11 @@
 红烧。烹饪结束，出锅装盘即可享用。</t>
         </is>
       </c>
-      <c r="E264" s="16" t="n"/>
+      <c r="E264" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、西餐风味、咸、酒香、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="48" customHeight="1" s="10">
       <c r="B265" s="13" t="inlineStr">
@@ -6337,7 +6445,11 @@
           <t>第1步：食材准备；第2步：取一汤锅加入适量清水，打开方太灶蒸烤烹饪机，大火烧煮至水沸后下入汤圆；第3步：烧煮3-4分钟捞出汤圆过凉水备用；第4步：打开烹饪机，选择空气炸模式，设置：180℃，12分钟，开始预热；第5步：将冷却好的汤圆均匀地裹上面包糠；第6步：用牙签在裹好面包糠的汤圆上戳几个小孔；第7步：将处理好的汤圆均匀的放在铺有烘焙纸的蒸烤盘上；第8步：将蒸烤盘放入预热好的烹饪机中层，烹饪结束后取出即可享用</t>
         </is>
       </c>
-      <c r="E273" s="14" t="n"/>
+      <c r="E273" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、元宵、甜、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="48" customHeight="1" s="10">
       <c r="B274" s="15" t="inlineStr">
@@ -6509,7 +6621,11 @@
           <t>第1步：食材准备；第2步：土豆去皮切小粒，葱切碎，姜切末；第3步：猪肉馅中放料酒、盐、放有机生抽、加入葱姜末、白糖；第4步：放土豆粒，再放黄豆酱拌匀；第5步：将拌匀的猪肉馅儿放到蒸碗里再放入小米椒；第6步：放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第7步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E281" s="14" t="n"/>
+      <c r="E281" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、川湘菜、辣、微辣、香辣、咸、上班族、咸鲜 | 、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="48" customHeight="1" s="10">
       <c r="B282" s="15" t="inlineStr">
@@ -6529,7 +6645,7 @@
       </c>
       <c r="E282" s="16" t="inlineStr">
         <is>
-          <t>耗时长、汤类</t>
+          <t>午餐、晚餐、粤菜、清淡、鲜美、更年期、老人、哺乳、贫血、耗时长、汤类、家常菜</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7193,11 @@
           <t>第1步：紫苏辣子鸡无需解冻，摆放在铺有硅油纸的蒸烤盘上。；第2步：打开方太智能烹饪设备，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E307" s="14" t="n"/>
+      <c r="E307" s="14" t="inlineStr">
+        <is>
+          <t>晚餐、川湘菜、辣、香辣、咸、上班族、烤制类</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="48" customHeight="1" s="10">
       <c r="B308" s="15" t="inlineStr">
@@ -7207,7 +7327,7 @@
       </c>
       <c r="E313" s="14" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>午餐、晚餐、粤菜、清淡、鲜美、哺乳、更年期、耗时长、家常菜</t>
         </is>
       </c>
     </row>
@@ -7315,7 +7435,11 @@
           <t>第1步：食材准备；第2步：奶油奶酪室温软化至无颗粒，加入淡奶油和糖，用电动打蛋器打发至六分成光滑状态；第3步：放入摸具冻成冰块；第4步：除黄油外的所有材料混合，粉类先过筛，搅拌成糊状。可以再过一次筛，保证液体无颗粒；第5步：包上保鲜膜，放入方太蒸箱，设置普通蒸模式，100度，蒸20分钟即可；第6步：蒸好后取出，趁热放入黄油，戴手套揉面至黄油全部被吸收，分成4个小团子，擀成薄皮；第7步：放入冻好的馅料，收口成团；第8步：表面筛一层可可粉即可；第9步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E318" s="16" t="n"/>
+      <c r="E318" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、西餐风味、甜、甜点、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="48" customHeight="1" s="10">
       <c r="B319" s="13" t="inlineStr">
@@ -7333,7 +7457,11 @@
           <t>第1步：白菜去根，取大叶子备用。；第2步：肉糜放入碗中，加入蟹黄、鸡蛋、盐、糖和葱姜水搅打上劲制成肉馅备用。；第3步：煮一锅开水，把白菜叶汆烫15秒，捞出备用。；第4步：把煮过的菜叶子摊开，放入肉馅儿在前三分之一的地方。；第5步：把菜叶子左右两边叠起，再从上往下慢慢卷起，放在盘中再放上蒸烤盘备用。；第6步：打开蒸烤一体机，将蒸烤盘放在蒸烤一体机第 2层，开启电源，选择”开始烹饪”按键，按屏幕提示操作；第7步：拿出，把蒸完的水倒入锅中，加入枸杞煮开后加入水淀粉勾芡。</t>
         </is>
       </c>
-      <c r="E319" s="14" t="n"/>
+      <c r="E319" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、清淡、鲜美、儿童、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="48" customHeight="1" s="10">
       <c r="B320" s="15" t="inlineStr">
@@ -7529,7 +7657,7 @@
       </c>
       <c r="E328" s="16" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>下午茶、地方风味、咸、辣、香辣、烤制类</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7921,7 @@
       </c>
       <c r="E340" s="16" t="inlineStr">
         <is>
-          <t>汤类</t>
+          <t>午餐、晚餐、粤菜、清淡、更年期、老人、养胃、汤类</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7963,11 @@
           <t>第1步：将300g牛肉切成小块，香菜切末。；第2步：将切好的牛肉放入碗中，加入食盐、五香粉、辣椒粉、孜然粒、芝麻和橄榄油，用手抓匀，腌制10分钟。；第3步：将腌制好的牛肉粒摆放在铺有锡纸的烤盘上，均匀地撒上芝麻。；第4步：将300g牛肉切成薄片，生姜切片，大葱切片，小葱切末，蒜切片，香芋切块备用。；第5步：将牛肉片放入碗中，加入白砂糖、淀粉、蚝油、生抽、老抽，放入姜片、葱片、蒜片，加入食用油，用手抓匀。；第6步：将香芋铺在盘子底部，将腌制好的牛肉片平铺在香芋上。；第7步：开启电源，将孜然牛肉粒放入第5层，将香芋蒸牛肉放入第2层，选择“开始烹饪”按键，按屏幕提示操作。；第8步：烹饪完成取出。在香芋蒸牛肉上撒上葱花，浇上热油即可。；第9步：将烤好的孜然牛肉粒摆盘，撒香菜装饰即可。</t>
         </is>
       </c>
-      <c r="E342" s="16" t="n"/>
+      <c r="E342" s="16" t="inlineStr">
+        <is>
+          <t>晚餐、川湘菜、咸、辣、香辣、上班族、贫血</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="48" customHeight="1" s="10">
       <c r="B343" s="13" t="inlineStr">
@@ -7853,7 +7985,11 @@
           <t>第1步：食材准备；第2步：用清水把香菇洗净，去蒂，对剖成两半；第3步：用清水把嫩鸡冲洗干净，斩成小块；第4步：把鸡肉块、香菇、葱段、姜片放入汤碗中，加入盐、酱油、料酒、胡椒粉、白糖、香油、水淀粉，用手抓匀；第5步：放入方太C2.i智能蒸箱，过温蒸模式，110度蒸30分钟左右,直至鸡肉熟烂即可；第6步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E343" s="14" t="n"/>
+      <c r="E343" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、粤菜、清淡、鲜美、儿童、老人、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="48" customHeight="1" s="10">
       <c r="B344" s="15" t="inlineStr">
@@ -8377,7 +8513,11 @@
           <t>第1步：1</t>
         </is>
       </c>
-      <c r="E367" s="14" t="n"/>
+      <c r="E367" s="14" t="inlineStr">
+        <is>
+          <t>早餐、西餐风味、奶香</t>
+        </is>
+      </c>
     </row>
     <row r="368" ht="48" customHeight="1" s="10">
       <c r="B368" s="15" t="inlineStr">
@@ -8397,7 +8537,7 @@
       </c>
       <c r="E368" s="16" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>早餐、儿童、老人、养胃、助眠、贫血、便秘、耗时长</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8603,7 @@
       </c>
       <c r="E371" s="14" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>早餐、午餐、粤菜、咸、上班族、耗时长、家常菜</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8755,11 @@
           <t>第1步：把糯米洗净，放入水中浸泡4小时，沥干备用；第2步：猪肉洗净剁成肉糜，葱姜切末；第3步：猪肉糜和葱姜放入碗内，加料酒、盐、淀粉、生抽搅拌均匀；第4步：把肉馅挤成大小合适的丸子，每个肉丸子上裹上一层糯米；第5步：锅中放适量的冷水，蒸屉上铺一层干净纱布，将裹好的糯米丸子放在纱布上，大火蒸20分钟即可；第6步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E378" s="16" t="n"/>
+      <c r="E378" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、中式面点、清淡、咸、儿童、老人、养胃</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="48" customHeight="1" s="10">
       <c r="B379" s="13" t="inlineStr">
@@ -8677,7 +8821,11 @@
           <t>第1步：食材准备；第2步：把紫薯洗净，之后放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第3步：紫薯去皮切块放凉备用，加入20毫升水用勺子压成紫薯泥；第4步：紫薯泥装入另一个有保鲜膜的碗中；第5步：再倒扣入盘子，用手整成一个圆平乎的形状；第6步：淋上的低脂酸奶，最后撒上薯片碎即可；第7步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E381" s="14" t="n"/>
+      <c r="E381" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、甜、儿童、老人、便秘、减脂</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="48" customHeight="1" s="10">
       <c r="B382" s="15" t="inlineStr">
@@ -8697,7 +8845,7 @@
       </c>
       <c r="E382" s="16" t="inlineStr">
         <is>
-          <t>汤类</t>
+          <t>午餐、晚餐、清淡、更年期、老人、养胃、粤菜、江浙菜、鲜美、健胃消食 | 汤类</t>
         </is>
       </c>
     </row>
@@ -8981,7 +9129,11 @@
           <t>第1步：将8只大闸蟹洗净后，放入方太灶蒸烤烹饪机中层，选择普通蒸模式，设置：100°C，15分钟，开始蒸制。；第2步：蒸制结束取出大闸蟹放凉，拆出蟹黄和蟹肉，将蟹壳洗刷干净备用。；第3步：取1锅大火档热锅，下入食用油，油温5成时下入姜片，爆香后捞出姜片。；第4步：接着下入蟹黄和蟹肉，转小火煸炒出红润的蟹油后，加入1克盐、生抽、香醋、白砂糖、黄酒和葱花，炒出香味。；第5步：将炒好的蟹黄酱盛出备用，锅中留少许蟹黄油，再次热锅，下入虾肉丁煸炒至断生即可盛出。；第6步：橙子用小刀以锯齿状花刀将橙子顶揭下，挖出橙肉留橙子壳当容器，取橙肉30克切成小丁备用。；第7步：在两个橙子壳中分别加入15克橙肉，填入蟹黄酱至8分满，盖上橙子顶，放在蒸烤架上。开启电源，取出水箱加满水，将蒸烤架放入烹饪机，选择【开始烹饪】按键，按屏幕提示操作即可</t>
         </is>
       </c>
-      <c r="E395" s="14" t="n"/>
+      <c r="E395" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、鲜美、咸、上班族、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="396" ht="48" customHeight="1" s="10">
       <c r="B396" s="15" t="inlineStr">
@@ -9243,7 +9395,7 @@
       </c>
       <c r="E407" s="14" t="inlineStr">
         <is>
-          <t>汤类</t>
+          <t>午餐、晚餐、江浙菜、清淡、鲜美、老人、减脂、汤类、家常菜</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9525,11 @@
           <t>第1步：将虾去头剥壳，留尾巴，把虾肚子切开，但背部不要切断，并去除虾线。；第2步：将处理好的虾放入料理盆中，加入原料B中的材料，用手抓匀，腌制10分钟。；第3步：将腌制好的虾先用淀粉裹匀，再裹上鸡蛋液，最后表面粘满面包糠。；第4步：在烤盘上铺烘焙纸，将处理好的虾平铺在烤盘上，表面刷色拉油，撒上适量的黑胡椒粉。；第5步：把烤盘放入机器中间层，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E413" s="14" t="n"/>
+      <c r="E413" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、地方风味、咸、脆、香脆、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="414" ht="48" customHeight="1" s="10">
       <c r="B414" s="15" t="inlineStr">
@@ -9391,7 +9547,11 @@
           <t>第1步：将三黄鸡剁块；洋葱切块；葱绿和红辣椒切丝；备用。；第2步：将洗净的三黄鸡块擦干水分，加入40g生抽、15g老抽、15g蚝油、15g米酒、2小勺盐、2小勺白糖和1小勺白胡椒粉，充分搅拌均匀后放入冰箱冷藏腌制1小时。；第3步：海豚微压锅中加入50g食用油、50g姜片、50g葱白段、50g蒜瓣和洋葱块，设置：3分钟/一键大火，进行煸炒。；第4步：将腌好的鸡块均匀码入锅中，并淋上腌鸡料，；第5步：盖上锅盖并关闭气阀，设置：30分钟/恒温模式-无水焖，进行焖炖。</t>
         </is>
       </c>
-      <c r="E414" s="16" t="n"/>
+      <c r="E414" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、咸、咸香、老人、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="415" ht="48" customHeight="1" s="10">
       <c r="B415" s="13" t="inlineStr">
@@ -9541,7 +9701,11 @@
           <t>第1步：将坚果切碎备用。；第2步：揉面：在搅拌盆中依次称入水（水温= 56℃-（面粉温度+室温））、酵母、蜂蜜、盐、T65面粉、全麦面粉低速搅拌至面团光滑，具有一定延展性，加入橄榄油、混合坚果、混合果干低速搅拌使其混合即可。；第3步：一次发酵：在保鲜盒内喷少许脱模油，将面团转移至保鲜盒内用手稍稍按压使之均匀分布，放在烹饪机中35℃发酵70~90分钟。；第4步：分割：在台面上撒上少许干粉，将保鲜盒倒扣使面团平铺在台面上，用刮板整齐分割面团为4份。；第5步：预整形：取出面团，将面团光滑面向下，用手轻拍使面团排气，左手手轻捏起面团右上角，右手虎口按压使面团在上下1/2处收口，继续翻折（推）收口，呈筒状。；第6步：中间醒发：台面上撒少许干粉，在面团表面盖保鲜袋，室温醒发20分钟。（室温即可）；第7步：整形：将面团轻轻揉搓至长条状；第8步：最后发酵：整形完毕的面团放在撒有干粉的发酵布上，收口朝上，相邻间隔以发酵布折叠隔开，放在烹饪机中35℃发酵30-45分钟左右。；第9步：撒粉：使用面团转移板将面团收口朝下转移到垫有烘焙纸的蒸烤盘上，使用面粉筛在面包表面均匀筛上适量干粉。；第10步：发酵结束前10分钟，先预热蒸烤箱。开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E421" s="14" t="n"/>
+      <c r="E421" s="14" t="inlineStr">
+        <is>
+          <t>早餐、西餐风味、甜、上班族、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="48" customHeight="1" s="10">
       <c r="B422" s="15" t="inlineStr">
@@ -9757,7 +9921,11 @@
           <t>第1步：食材准备；第2步：腌制排骨：排骨洗净后切小段，加料酒、蚝油、白糖、生粉、白胡椒粉搅拌均匀，再加入几片柠檬增香提味；第3步：处理芋头：芋头去皮，切成和排骨大小差不多的均匀块状；第4步：?方太CS34BW磁控电磁灶调至9段大火，油煎芋头至两面金黄；第5步：方太C2.i智能蒸箱普通蒸模式，预热至100℃；第6步：将芋头排列在碗底，铺上排骨，最上面一层淋上剁椒；第7步：放入蒸箱，普通蒸模式，100℃，20分钟；第8步：淋油：香葱爆油，淋在所有食材表面，激发出剁椒的香味即可；第9步：尽情享用吧</t>
         </is>
       </c>
-      <c r="E431" s="14" t="n"/>
+      <c r="E431" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、川湘菜、辣、微辣、咸、上班族、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="432" ht="48" customHeight="1" s="10">
       <c r="B432" s="15" t="inlineStr">
@@ -10702,7 +10870,11 @@
           <t>第1步：黄彩椒切粒，加入盐2g、白酒拌匀腌制半小时后，沥干水分备用。；第2步：锅中倒入色拉油，放入蒜泥炒香，在放入腌拌好的黄彩椒粒、黄灯笼辣椒酱及其余调料炒匀即可。；第3步：鲜鱿鱼洗净后，改刀。；第4步：开水中汆烫一下（去腥）。；第5步：装盘备用，铺上一层熬制好的黄椒酱，将盘子放在蒸烤架上。；第6步：打开蒸烤一体机，将蒸烤架放入蒸烤一体机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。；第7步：取出，撒上葱花，淋上热油。</t>
         </is>
       </c>
-      <c r="E474" s="16" t="n"/>
+      <c r="E474" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、川湘菜、辣、海鲜风味、鲜美、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="475" ht="48" customHeight="1" s="10">
       <c r="B475" s="13" t="inlineStr">
@@ -11030,7 +11202,7 @@
       </c>
       <c r="E489" s="14" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>午餐、晚餐、粤菜、清淡、鲜美、老人、养胃、耗时长</t>
         </is>
       </c>
     </row>
@@ -11118,7 +11290,7 @@
       </c>
       <c r="E493" s="14" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>早餐、下午茶、粤菜、清淡、甜、儿童、哺乳、老人、耗时长</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11310,11 @@
           <t>第1步：将香菇 豆腐干 春笋切丁备用；第2步：将糯米粉 粘米粉 木薯淀粉 艾草粉倒入盆中 搅拌均匀；第3步：分次加入水；第4步：揉至面团表面光滑即可；第5步：取50克左右的面团 放入沸水中煮熟；第6步：趁热放入之前的面团中揉搓均匀；第7步：将面团盖上保鲜膜备用；第8步：取锅倒油；第9步：打开方太磁控电磁灶 调至6档；第10步：将猪肉末倒入锅中 炒至变色；第11步：放入切好的豆腐干 春笋 香菇 咸菜；第12步：放入花椒粉 胡椒粉 白糖 食盐 翻炒至变熟 出锅备用；第13步：将准备好的面团搓成长条；第14步：分成40克的面剂子；第15步：使用擀面杖擀成圆片 放入炒好的馅料；第16步：将面皮捏成粿子；第17步：可以根据喜好将清明粿捏成不同的形状；第18步：放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第19步：蒸制完成 取出粿子即可</t>
         </is>
       </c>
-      <c r="E494" s="16" t="n"/>
+      <c r="E494" s="16" t="inlineStr">
+        <is>
+          <t>清明节、早餐、中式面点、咸、香</t>
+        </is>
+      </c>
     </row>
     <row r="495" ht="48" customHeight="1" s="10">
       <c r="B495" s="13" t="inlineStr">
@@ -11442,7 +11618,11 @@
           <t>第1步：主锅中加入高筋面粉、细砂糖、盐、蛋清、奶粉、酵母和牛奶，盖上锅盖和量杯，设置：5分钟/揉面。；第2步：加入软化黄油，盖上锅盖和量杯，设置：7分钟/揉面。烹饪结束，将面团取出折叠至表面光滑，放入料理盆中封上保鲜膜发酵至两倍大。</t>
         </is>
       </c>
-      <c r="E508" s="16" t="n"/>
+      <c r="E508" s="16" t="inlineStr">
+        <is>
+          <t>早餐、下午茶、西餐风味、甜、奶香、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="509" ht="48" customHeight="1" s="10">
       <c r="B509" s="13" t="inlineStr">
@@ -11572,7 +11752,7 @@
       </c>
       <c r="E514" s="16" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>晚餐、粤菜、咸、鲜美、老人、更年期、耗时长</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11772,11 @@
           <t>第1步：主锅中加入食用油、姜片、大葱段、大蒜片、草果、豆蔻、陈皮、八角、桂皮、干辣椒段、香叶、花椒和辣椒酱，设置：3分钟/9档，持续翻炒。；第2步：加入洗净的小龙虾、生抽、蚝油、盐和啤酒，盖上锅盖，设置：15分钟/5档，适时翻炒。烹饪结束，撒上葱段和10g蒜末，翻炒拌匀，盛出即可享用。</t>
         </is>
       </c>
-      <c r="E515" s="14" t="n"/>
+      <c r="E515" s="14" t="inlineStr">
+        <is>
+          <t>晚餐、川湘菜、江浙菜、辣、香辣、咸、鲜美、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="516" ht="48" customHeight="1" s="10">
       <c r="B516" s="15" t="inlineStr">
@@ -11610,7 +11794,11 @@
           <t>第1步：海豚微压锅中放入蒸架，加入800g水，将2只大闸蟹放在倒放在蒸架上，再放上15g姜片，设置：15分钟/一键大火。；第2步：盖上锅盖并关闭气阀，进行蒸制。；第3步：蒸制结束取出大闸蟹放凉，拆出蟹黄和蟹肉，将蟹壳洗刷干净备用。；第4步：海豚微压锅中加入食用油、蟹壳&amp;蟹脚和30g姜片；第5步：设置：3分钟/7档，进行煸炒。结束后捞出姜片和蟹壳&amp;蟹脚。；第6步：海豚微压锅中加入蟹黄和蟹肉、盐、生抽、香醋、白砂糖、花雕酒和葱花；第7步：设置：5分钟/6档，进行煸炒，炒出香味。快结束前加入水淀粉勾芡；第8步：橙子用小刀以锯齿状花刀将橙子顶揭下，挖出橙肉留橙子壳当容器，取橙肉30克切成小丁备用。；第9步：海豚微压锅中放入蒸架，将两个橙子壳中分别加入15克橙肉，填入蟹黄酱至8分满，盖上橙子顶，放在蒸架上，加入500g水。；第10步：盖上锅盖并关闭气阀，设置：8分钟/一键大火，进行蒸制。</t>
         </is>
       </c>
-      <c r="E516" s="16" t="n"/>
+      <c r="E516" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、鲜美、咸、上班族、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="517" ht="48" customHeight="1" s="10">
       <c r="B517" s="13" t="inlineStr">
@@ -11848,7 +12036,11 @@
           <t>第1步：羊肉切0.5cm的小粒备用，姜末和大葱段加入水中备用。；第2步：把羊肉放入碗中 一点点加入葱姜水，慢慢搅打上劲。；第3步：再在羊肉里加入生粉、生抽、盐、味精和胡椒粉搅拌均匀，腌制30分钟备用。；第4步：皮子扣成圆形，包入25g的馅，转圈慢慢收口。；第5步：打开蒸烤一体机，将烤架放在蒸烤一体机第 2层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E527" s="14" t="n"/>
+      <c r="E527" s="14" t="inlineStr">
+        <is>
+          <t>早餐、午餐、地方风味、中式面点、咸、鲜美、养胃、老人</t>
+        </is>
+      </c>
     </row>
     <row r="528" ht="48" customHeight="1" s="10">
       <c r="B528" s="15" t="inlineStr">
@@ -12022,7 +12214,7 @@
       </c>
       <c r="E535" s="14" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>午餐、晚餐、西餐风味、咸、酸、儿童、上班族、耗时长</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12280,7 @@
       </c>
       <c r="E538" s="16" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>早餐、甜、老人、儿童、养胃、助眠、贫血、耗时长</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12698,7 @@
       </c>
       <c r="E557" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、江浙菜、咸、鲜美、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -12856,7 +13048,11 @@
           <t>第1步：食材准备；第2步：将150克面粉，20克菠菜粉，80毫升水，10克糖，2克酵母、10毫升油搅拌均匀揉成光滑的面团 ，150克面粉，80毫升水，10克糖，2克酵母搅拌均匀揉成光滑的面团 ，都发酵至两倍大，之后将菠菜面团揉搓排气，擀成面片，用模具，压出圆形；第3步：面片对折，用模具压出一个下弦月的形状；第4步：白色面团，一样揉匀排气，分别搓成多个小球状；第5步：然后白色小圆，撒上水，放在菠菜面皮上；第6步：之后像捏饺子一样，两边捏合起来封底，正面呈豌豆状；第7步：放入方太蒸箱，设置普通蒸模式，100度，蒸10分钟即可；第8步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E573" s="14" t="n"/>
+      <c r="E573" s="14" t="inlineStr">
+        <is>
+          <t>早餐、中式面点、甜、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="574" ht="48" customHeight="1" s="10">
       <c r="B574" s="15" t="inlineStr">
@@ -13249,7 +13445,11 @@
           <t>第1步：A食材准备；第2步：糯米粉中加玉米淀粉、白糖、抹茶粉搅拌匀匀后加牛奶搅拌至无颗粒 ；第3步：模具中刷油撒蜜豆；第4步：倒入糯米糊；第5步：放入方太蒸箱，选择普通蒸模式，100度蒸20分钟，不烫手时脱模即可；第6步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E591" s="14" t="n"/>
+      <c r="E591" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、中式面点、甜、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="592" ht="48" customHeight="1" s="10">
       <c r="B592" s="15" t="inlineStr">
@@ -13443,7 +13643,11 @@
           <t>第1步：将龙虾处理好，对半剖开。；第2步：烤龙虾准备：蒸烤盘上铺锡纸，摆上龙虾，在虾肉表面淋少量沙拉酱，再铺上一层芝士丝。；第3步：开启电源，取出水箱加满水，将蒸烤盘放入烹饪机中间层，选择【开始烹饪】按键，按屏幕提示操作即可。</t>
         </is>
       </c>
-      <c r="E600" s="16" t="n"/>
+      <c r="E600" s="16" t="inlineStr">
+        <is>
+          <t>晚餐、西餐风味、奶香、咸、鲜美、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="601" ht="48" customHeight="1" s="10">
       <c r="B601" s="13" t="inlineStr">
@@ -13571,7 +13775,11 @@
           <t>第1步：雪梨洗净后去皮，切成6厘米x1厘米的粗条。；第2步：取1大碗，将雪梨条放入清水浸泡备用。；第3步：牛小排肉切薄片。；第4步：牛小排薄片放入碗中，加入生抽、蚝油、白糖、黑胡椒碎和淀粉，搅拌均匀。；第5步：取1碗，将雪梨条放在碗底，将牛小排薄片码放在雪梨条上。；第6步：将装有雪梨牛小排的碗，放在蒸烤架中。放入蒸烤箱中间层，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E606" s="16" t="n"/>
+      <c r="E606" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、咸、鲜美、养胃</t>
+        </is>
+      </c>
     </row>
     <row r="607" ht="48" customHeight="1" s="10">
       <c r="B607" s="13" t="inlineStr">
@@ -13633,7 +13841,11 @@
           <t>第1步：清洗芋头，去皮后浸入清水，点入白醋，防止芋头表面氧化。；第2步：大蒜切末，加剁椒酱、蚝油、生抽、糖，充分搅拌均匀，制成酱汁。；第3步：芋头沥干，码放盘中，淋上酱汁，确保每一颗芋头都裹满酱汁。；第4步：把盘子放在蒸烤盘上。；第5步：打开方太灶蒸烤烹饪机，将蒸烤架放在烹饪机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作；第6步：淋上热油。</t>
         </is>
       </c>
-      <c r="E609" s="14" t="n"/>
+      <c r="E609" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、川湘菜、辣、微辣、咸、老人、养胃、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="610" ht="48" customHeight="1" s="10">
       <c r="B610" s="15" t="inlineStr">
@@ -13651,7 +13863,11 @@
           <t>第1步：取出冷鲜调味法式羊排，放在铺有锡箔纸的蒸烤盘上；第2步：打开方太智能烹饪设备，将蒸烤盘放入设备中间层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E610" s="16" t="n"/>
+      <c r="E610" s="16" t="inlineStr">
+        <is>
+          <t>晚餐、西餐风味、咸、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="611" ht="48" customHeight="1" s="10">
       <c r="B611" s="13" t="inlineStr">
@@ -13691,7 +13907,11 @@
           <t>第1步：鲍鱼洗净后加上葱姜。；第2步：打开方太集成烹饪设备，将蒸烤架放入烹饪机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。；第3步：取出后入冷水浸泡。；第4步：去壳去内脏，切成小条。；第5步：香椿焯水后捞出，挤干水分。；第6步：切成末。；第7步：加上盐、糖、鸡粉调味。；第8步：麻油倒入锅中烧至六成热。；第9步：浇在香椿上，做成香椿酱。；第10步：把切好的鲍鱼加入香椿酱拌匀。</t>
         </is>
       </c>
-      <c r="E612" s="16" t="n"/>
+      <c r="E612" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、地方风味、清淡、鲜美、老人</t>
+        </is>
+      </c>
     </row>
     <row r="613" ht="48" customHeight="1" s="10">
       <c r="B613" s="13" t="inlineStr">
@@ -13799,7 +14019,7 @@
       </c>
       <c r="E617" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>午餐、晚餐、西餐风味、咸、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -13973,7 +14193,11 @@
           <t>第1步：料理盆中加入花菜末、胡萝卜末、玉米粒、青豆粒、胡椒碎、1g盐、橄榄油、生抽，充分搅拌均匀后放入盘中。；第2步：将盘放在蒸烤架上，放入机器中间层，设置加湿烤210℃，7分钟。期间到达设定温度时，开门翻拌一次；第3步：取一平底锅，加入少许油，将腌制好的牛肉粒和鸡胸肉丁炒制成熟后</t>
         </is>
       </c>
-      <c r="E625" s="14" t="n"/>
+      <c r="E625" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、清淡、减脂、便秘、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="626" ht="48" customHeight="1" s="10">
       <c r="B626" s="15" t="inlineStr">
@@ -14167,7 +14391,11 @@
           <t>第1步：将沃柑剥去外皮。；第2步：将沃柑分成小瓣并去籽。；第3步：将沃柑摆放在烤架上。；第4步：打开方太智能烹饪设备，取出水箱加满水，将蒸烤架放入蒸烤箱第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E634" s="16" t="n"/>
+      <c r="E634" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、甜、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="635" ht="48" customHeight="1" s="10">
       <c r="B635" s="13" t="inlineStr">
@@ -15440,7 +15668,11 @@
           <t>第1步：食材准备；第2步：碗中加入紫薯泥和白糖搅拌均匀制成馅料备用；第3步：碗中加入牛奶、玉米油、糯米粉、粘米粉、澄粉、抹茶粉、糖粉搅拌均匀制成面团备用；第4步：放入方太F1蒸箱，选择普通蒸模式，100度，20分钟放入面团蒸熟，蒸熟后放凉备用；第5步：分成每个25克的小面团，放入紫薯馅，搓成圆备用；第6步：将包好的月饼放入模具压出形状即可，烹饪完成即可食用；第7步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E692" s="16" t="n"/>
+      <c r="E692" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、中秋、甜、甜点、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="693" ht="48" customHeight="1" s="10">
       <c r="B693" s="13" t="inlineStr">
@@ -15766,7 +15998,11 @@
           <t>第1步：食材准备；第2步：方太电磁灶开小火1-2档，牛奶中放入黄油；第3步：放入糖；第4步：加入奶油；第5步：再放入奶酪片；第6步：然后用筷子均匀地搅拌，?一直到所有的辅料都融化且没有颗粒；第7步：熬煮的辅料中，加入蜂蜜；一边用筷子慢慢搅拌，一边缓缓倒入蜂蜜；第8步：一直搅拌到停下筷子后，锅里咕咚咕咚冒泡，变成膏状；第9步：用勺子轻轻的将调好的奶酪液均匀的涂抹在面包的上面；第10步：打开方太智能烹饪设备，将蒸烤盘放入第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作；第11步：尽情享用美味的网红熔岩吐司吧</t>
         </is>
       </c>
-      <c r="E707" s="14" t="n"/>
+      <c r="E707" s="14" t="inlineStr">
+        <is>
+          <t>早餐、下午茶、甜、甜点、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="708" ht="48" customHeight="1" s="10">
       <c r="B708" s="15" t="inlineStr">
@@ -15808,7 +16044,7 @@
       </c>
       <c r="E709" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、川湘菜、辣、香辣、咸、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -15872,7 +16108,11 @@
           <t>第1步：蛏子焯水。；第2步：取肉洗干净，放入盘中备用。；第3步：切葱花，小米椒切圈，姜切丝。；第4步：取一碗，把酒酿、黄酒、蒸鱼豉油调匀。；第5步：把料汁浇在蛏子肉上，撒上姜丝。；第6步：打开蒸烤一体机，将蒸烤架放在蒸烤一体机第 2层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。；第7步：撒上葱花和小米椒，浇上热油。</t>
         </is>
       </c>
-      <c r="E712" s="16" t="n"/>
+      <c r="E712" s="16" t="inlineStr">
+        <is>
+          <t>晚餐、海鲜风味、鲜美、酒香、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="713" ht="48" customHeight="1" s="10">
       <c r="B713" s="13" t="inlineStr">
@@ -16068,7 +16308,7 @@
       </c>
       <c r="E721" s="14" t="inlineStr">
         <is>
-          <t>汤类</t>
+          <t>下午茶、甜、儿童、老人、更年期、养胃、助眠、贫血、汤类</t>
         </is>
       </c>
     </row>
@@ -16418,7 +16658,11 @@
           <t>第1步：食材准备；第2步：将土豆放入方太F1蒸箱中，选择普通蒸模式，设置100度，20分钟；第3步：方太燃气灶大火7档加入水，水开放入玉米粒煮至断生盛出备用；第4步：锅中继续加入藜麦煮10分钟盛出备用；第5步：蒸好的土豆压成泥状，加入生抽、黑胡椒粉、玉米粒和藜麦均匀搅拌；第6步：黄瓜切片摆入盘底，把土豆泥整成球状放上黄瓜片，即可食用；第7步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E737" s="14" t="n"/>
+      <c r="E737" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、清淡、减脂、便秘、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="738" ht="48" customHeight="1" s="10">
       <c r="B738" s="15" t="inlineStr">
@@ -16568,7 +16812,11 @@
           <t>第1步：锅中放入少许色拉油，打开方太磁控电磁灶，调至6档中火，将油烧热，放入鲜青花椒、烧椒酱爆香，加入少许清水，放入鸡汁、蒸鱼豉油、白砂糖，制作成酱汁备用。；第2步：将韭菜烫熟备用。；第3步：春笋放入开水中煮熟捞出。将煮熟的春笋切成粗丝，将莴笋也切成粗丝。；第4步：将厚百叶切成宽度为5厘米，长10厘米的片，放入开水中烫一下。；第5步：将烫好的百叶片铺平，包入春笋丝、莴笋丝、蛏肉后卷起，用韭菜扎紧。；第6步：开启电源，将百叶卷放入设备第2层，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E744" s="16" t="n"/>
+      <c r="E744" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、清淡、鲜美、上班族、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="745" ht="48" customHeight="1" s="10">
       <c r="B745" s="13" t="inlineStr">
@@ -16630,7 +16878,11 @@
           <t>第1步：土鸡放入碗中 倒入清水 将土鸡清洗干净 洗净后捞出切块备用；第2步：将生姜切片 葱切段；第3步：取锅 将切好的鸡块放入锅中 放入姜片 葱段和料酒 倒入清水；第4步：打开方太磁控电磁灶 调至6档中火；第5步：煮沸后用勺子撇去浮沫；第6步：捞出鸡块 沥干水分 将鸡块放入碗中；第7步：加入食盐 白胡椒粉 花椒粉 香油和生抽 用手抓匀；第8步：放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第9步：蒸制完成取出 撒上葱花即可享用</t>
         </is>
       </c>
-      <c r="E747" s="14" t="n"/>
+      <c r="E747" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、地方风味、清淡、鲜美、老人、哺乳</t>
+        </is>
+      </c>
     </row>
     <row r="748" ht="48" customHeight="1" s="10">
       <c r="B748" s="15" t="inlineStr">
@@ -16868,7 +17120,11 @@
           <t>第1步：主锅中加入食用油、小葱段、姜片和蒜片，盖上锅盖，设置：1分钟/大火/热炒。；第2步：加入红咖喱、松板肉和料酒，盖上锅盖，设置：2分钟/大火/热炒。；第3步：加入西芹段、洋葱块、盐、白糖和鸡粉，盖上锅盖，设置：2分钟/大火/热炒。；第4步：加入水淀粉，盖上锅盖，设置：1分钟/大火/热炒。烹饪结束，出锅即可享用。</t>
         </is>
       </c>
-      <c r="E758" s="16" t="n"/>
+      <c r="E758" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、地方风味、辣、香辣、咸、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="759" ht="48" customHeight="1" s="10">
       <c r="B759" s="13" t="inlineStr">
@@ -16910,7 +17166,7 @@
       </c>
       <c r="E760" s="16" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、西餐风味、清淡、减脂、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -17370,7 +17626,11 @@
           <t>第1步：食材准备；第2步：锅里放油，油热放入咸菜丁、肉馅、笋丁一起翻炒熟备用分成10份放入冰箱冷冻2小时；第3步：将糯米粉、粘米粉、澄粉、色拉油混合在一起备用；第4步：之后将艾草粉和温水混合均匀倒入到糯米粉里，搅拌呈絮状，揉成光滑面团；第5步：将面团分成10等分，取一个面团，搓圆压扁，把咸菜笋丁肉馅包入其中；第6步：将青团放入方太蒸箱，设置普通蒸模式，100度，蒸10分钟即可；第7步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E781" s="14" t="n"/>
+      <c r="E781" s="14" t="inlineStr">
+        <is>
+          <t>清明节、早餐、中式面点、咸</t>
+        </is>
+      </c>
     </row>
     <row r="782" ht="48" customHeight="1" s="10">
       <c r="B782" s="15" t="inlineStr">
@@ -17522,7 +17782,7 @@
       </c>
       <c r="E788" s="16" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>早餐、西餐风味、清淡、减脂、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -17718,7 +17978,11 @@
           <t>第1步：主锅中加入食用油、芦笋段，盖上锅盖，设置：2分钟/大火/热炒。；第2步：加入水发羊肚菌、盐、鸡粉和高汤，盖上锅盖，设置：3分钟/大火/热炒。；第3步：加入百合瓣、淀粉水，设置：30秒/大火/热炒。烹饪结束，出锅装盘即可食用。</t>
         </is>
       </c>
-      <c r="E797" s="14" t="n"/>
+      <c r="E797" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、清淡、减脂、更年期、老人、养胃</t>
+        </is>
+      </c>
     </row>
     <row r="798" ht="48" customHeight="1" s="10">
       <c r="B798" s="15" t="inlineStr">
@@ -17934,7 +18198,11 @@
           <t>第1步：黑虎虾开背,去虾线备用。；第2步：黄皮果切半，去籽备用。；第3步：取一碗， 放入黑虎虾，加入生抽、盐和黄皮酱，搅拌均匀腌制十分钟。；第4步：取一烘焙纸,放上黄皮果和黑虎虾，把烘焙纸对折包住食材，封口，放上蒸烤架上备用。；第5步：打开蒸烤一体机，将烤架放在蒸烤一体机第2层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E807" s="14" t="n"/>
+      <c r="E807" s="14" t="inlineStr">
+        <is>
+          <t>晚餐、粤菜、海鲜风味、鲜美</t>
+        </is>
+      </c>
     </row>
     <row r="808" ht="48" customHeight="1" s="10">
       <c r="B808" s="15" t="inlineStr">
@@ -18174,7 +18442,7 @@
       </c>
       <c r="E818" s="16" t="inlineStr">
         <is>
-          <t>耗时长、汤类</t>
+          <t>午餐、晚餐、粤菜、清淡、更年期、老人、养胃、贫血、耗时长、汤类、家常菜</t>
         </is>
       </c>
     </row>
@@ -18304,7 +18572,11 @@
           <t>第1步：取一口奶锅，加入适量纯净水，放入鸡胸肉、香叶、姜片、花椒粒和料酒，水开煮5分钟。取出冷却，撕成鸡丝备用。；第2步：取一砂锅，加入洗净大米、玉米粒、胡萝卜丁和水，滴入几滴食用油，盖上锅盖。；第3步：打开蒸烤箱，将蒸烤架放入第二层，按屏幕提示操作。；第4步：结束后开门，加入鸡丝和香芹丁，搅拌均匀后，再设置全开烤180℃，15分钟。</t>
         </is>
       </c>
-      <c r="E824" s="16" t="n"/>
+      <c r="E824" s="16" t="inlineStr">
+        <is>
+          <t>早餐、清淡、儿童、老人、养胃、便秘</t>
+        </is>
+      </c>
     </row>
     <row r="825" ht="48" customHeight="1" s="10">
       <c r="B825" s="13" t="inlineStr">
@@ -18432,7 +18704,11 @@
           <t>第1步：取冷藏解冻后的调味法式羊排，放在垫有油纸的烤盘上，放入蒸烤一体机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E830" s="16" t="n"/>
+      <c r="E830" s="16" t="inlineStr">
+        <is>
+          <t>晚餐、西餐风味、咸、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="831" ht="48" customHeight="1" s="10">
       <c r="B831" s="13" t="inlineStr">
@@ -18450,7 +18726,11 @@
           <t>第1步：开洋用黄酒浸润，浸泡30分钟备用。；第2步：挑一条体型饱满的鳜鱼开花刀。；第3步：姜切片，葱切段，放入水中制成葱姜水。；第4步：把鳜鱼放入葱姜水中浸泡，可以去除鱼腥味。；第5步：取出鱼，放入干净的碗里，加入蛋清、盐、味粉和水淀粉，充分搅拌后，将碗放在蒸烤架上。；第6步：打开方太集成烹饪中心，将蒸烤架放在烹饪机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作，一键开启智能烹饪。；第7步：韭菜花切段。；第8步：和开洋一起放入锅中快火翻炒。；第9步：取出鱼，浇上韭菜花、开洋。</t>
         </is>
       </c>
-      <c r="E831" s="14" t="n"/>
+      <c r="E831" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、清淡、鲜美、儿童、养胃、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="832" ht="48" customHeight="1" s="10">
       <c r="B832" s="15" t="inlineStr">
@@ -18798,7 +19078,11 @@
           <t>第1步：食材准备；第2步：酵母加温水浸泡化开，静止5分钟；第3步：面粉中加入糖、盐、色拉油和混合好的酵母水搅拌成面絮，慢慢揉成光滑的面团；第4步：将和好的面团盖上保鲜膜，放在温暖的地方发酵，发酵至原来面团的2倍大后，揉面挤出里面的气泡；第5步：把面团挫成长条，平均分配成50克的面团；第6步：将面团擀成中间厚边缘薄的饼状；第7步：用包包子的方法把豆沙馅包进去，把包子依次排好放入蒸盘；第8步：醒30分钟之后，放入方太C2.i智能蒸箱，设置普通蒸模式，100度，蒸15分钟即可；第9步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E847" s="14" t="n"/>
+      <c r="E847" s="14" t="inlineStr">
+        <is>
+          <t>早餐、中式面点、甜、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="848" ht="48" customHeight="1" s="10">
       <c r="B848" s="15" t="inlineStr">
@@ -18972,7 +19256,7 @@
       </c>
       <c r="E855" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>下午茶、咸、香辣、脆、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19408,11 @@
           <t>第1步：香干斜刀切片，放入碗中用温水加2g盐浸泡30分钟。；第2步：红剁椒30g、蒜末10g、豆豉6g、白砂糖2g、生抽6g、老抽1g、猪油6g、纯净水25g混合均匀；第3步：将拌好的剁椒酱料铺在香干上。；第4步：取出水箱加满水，将盘子放入机器中间层。；第5步：启动机器，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E862" s="16" t="n"/>
+      <c r="E862" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、川湘菜、辣、咸、上班族、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="863" ht="48" customHeight="1" s="10">
       <c r="B863" s="13" t="inlineStr">
@@ -19166,7 +19454,7 @@
       </c>
       <c r="E864" s="16" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>早餐、下午茶、甜、儿童、老人、哺乳、养胃、助眠、耗时长</t>
         </is>
       </c>
     </row>
@@ -19254,7 +19542,7 @@
       </c>
       <c r="E868" s="16" t="inlineStr">
         <is>
-          <t>汤类</t>
+          <t>午餐、晚餐、清淡、鲜美、儿童、老人、养胃、减脂、汤类</t>
         </is>
       </c>
     </row>
@@ -19274,7 +19562,11 @@
           <t>第1步：食材准备；第2步：将鱼处理干净，鱼身上划几刀；第3步：葱切段，姜切片，姜片塞在鳃口淋上料酒；第4步：放上少许白糖和蒸鱼豉油；第5步：放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第6步：蒸鱼的水、姜片、葱段都倒掉，放入新鲜的姜丝和葱丝，热油浇淋在鱼身上即可；第7步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E869" s="14" t="n"/>
+      <c r="E869" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、清淡、鲜美、儿童、老人、上班族、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="870" ht="48" customHeight="1" s="10">
       <c r="B870" s="15" t="inlineStr">
@@ -19424,7 +19716,11 @@
           <t>第1步：食材准备；第2步：用水把碱融化；第3步：鸡蛋打散，倒入碱水混合均匀，再用勺子把泡沫撇出；第4步：碗中垫入油纸；第5步：倒入混合好的蛋液，再次撇去浮沫；第6步：放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第7步：切块，吃时加孜然、辣椒粉、蒜蓉酱、圆葱粒翻炒，超级美味；第8步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E876" s="16" t="n"/>
+      <c r="E876" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、东北菜、咸、香、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="877" ht="48" customHeight="1" s="10">
       <c r="B877" s="13" t="inlineStr">
@@ -19464,7 +19760,11 @@
           <t>第1步：将黄油放入盆中隔热水软化，加入鸡蛋液混合均匀。；第2步：将过筛后的茯苓粉、玉米淀粉及白砂糖加入黄油和鸡蛋液中充分搅拌，再加入低筋面粉揉成面团，静置10-15分钟。；第3步：面团放在硅油纸上，上面覆盖保鲜膜，用擀面杖压成薄片，用模具刻成特定形状，放入蒸烤盘中。；第4步：将蒸烤盘置于机器中间层，设置全开烤150℃，30分钟。</t>
         </is>
       </c>
-      <c r="E878" s="16" t="n"/>
+      <c r="E878" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、甜、儿童、老人、养胃</t>
+        </is>
+      </c>
     </row>
     <row r="879" ht="48" customHeight="1" s="10">
       <c r="B879" s="13" t="inlineStr">
@@ -19548,7 +19848,11 @@
           <t>第1步：主锅中加入冷冻的肉块，盖上锅盖和量杯，设置：10秒/10档切碎。烹饪结束，用刮刀将肉末取出即可使用。</t>
         </is>
       </c>
-      <c r="E882" s="16" t="n"/>
+      <c r="E882" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐</t>
+        </is>
+      </c>
     </row>
     <row r="883" ht="48" customHeight="1" s="10">
       <c r="B883" s="13" t="inlineStr">
@@ -19654,7 +19958,11 @@
           <t>第1步：取一烤盘，垫上油纸，刷上食用油，间隔摆上糍粑，放入蒸烤一体机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。；第2步：炸至表面金黄后，戴上硅胶手套取出烤盘，将糍粑翻面，重新放入蒸烤一体机，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E887" s="14" t="n"/>
+      <c r="E887" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、地方风味、甜、儿童、贫血</t>
+        </is>
+      </c>
     </row>
     <row r="888" ht="48" customHeight="1" s="10">
       <c r="B888" s="15" t="inlineStr">
@@ -19740,7 +20048,7 @@
       </c>
       <c r="E891" s="14" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>晚餐、地方风味、辣、奶香、鲜美、上班族、耗时长</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20598,7 @@
       </c>
       <c r="E916" s="16" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>晚餐、粤菜、咸、鲜美、老人、更年期、耗时长</t>
         </is>
       </c>
     </row>
@@ -20332,7 +20640,11 @@
           <t>第1步：黄鱼去骨，取鱼柳，切成厚片，抹上盐，腌制十分钟备用。；第2步：黄鱼放入盘中，把盘子放到蒸烤架上。；第3步：打开蒸烤一体机，将蒸烤架放在蒸烤一体机第 2层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。；第4步：把泡椒、泡姜、蒜粒，切碎备用。；第5步：藿香切丝，香菜切末，小葱切葱花备用。；第6步：取一锅，倒入油，加入豆瓣酱小火炒香。；第7步：加入蒜末、泡姜碎、和泡椒碎炒出香味，再加入番茄酱翻炒片刻。；第8步：加入水煮开，加入糖、藿香、香菜、小葱，再加入水淀粉勾芡，关火备用。；第9步：取出黄鱼，淋上汤汁。</t>
         </is>
       </c>
-      <c r="E918" s="16" t="n"/>
+      <c r="E918" s="16" t="inlineStr">
+        <is>
+          <t>晚餐、川湘菜、辣、酸、鲜美、上班族、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="919" ht="48" customHeight="1" s="10">
       <c r="B919" s="13" t="inlineStr">
@@ -20394,7 +20706,11 @@
           <t>第1步：将牛肉切成小块；第2步：将切好的牛肉放入碗中，加入食盐、五香粉、辣椒粉、孜然粒和橄榄油，用手抓匀，腌制10分钟。；第3步：将腌制好的牛肉粒摆放在铺有锡纸的烤盘上，均匀地撒上芝麻。开启电源，将孜然牛肉粒放入中间层，选择“开始烹饪”按键，按屏幕提示操作。；第4步：将烤好的孜然牛肉粒摆盘，撒香菜装饰即可。趁热享用美味吧。</t>
         </is>
       </c>
-      <c r="E921" s="14" t="n"/>
+      <c r="E921" s="14" t="inlineStr">
+        <is>
+          <t>晚餐、川湘菜、咸、辣、香辣、上班族、贫血、烤制类</t>
+        </is>
+      </c>
     </row>
     <row r="922" ht="48" customHeight="1" s="10">
       <c r="B922" s="15" t="inlineStr">
@@ -20678,7 +20994,7 @@
       </c>
       <c r="E934" s="16" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、粤菜、甜、咸、儿童、烤制类</t>
         </is>
       </c>
     </row>
@@ -20810,7 +21126,7 @@
       </c>
       <c r="E940" s="16" t="inlineStr">
         <is>
-          <t>耗时长、汤类</t>
+          <t>早餐、下午茶、甜、哺乳、贫血、更年期、老人、耗时长、汤类</t>
         </is>
       </c>
     </row>
@@ -20876,7 +21192,7 @@
       </c>
       <c r="E943" s="14" t="inlineStr">
         <is>
-          <t>耗时长、汤类</t>
+          <t>午餐、晚餐、粤菜、清淡、更年期、老人、养胃、耗时长、汤类</t>
         </is>
       </c>
     </row>
@@ -21028,7 +21344,11 @@
           <t>第1步：将腊汁肉夹馍解冻后，放在垫有油纸的烤盘上，放入蒸烤一体机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E950" s="16" t="n"/>
+      <c r="E950" s="16" t="inlineStr">
+        <is>
+          <t>早餐、午餐、地方风味、咸、香、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="951" ht="48" customHeight="1" s="10">
       <c r="B951" s="13" t="inlineStr">
@@ -21488,7 +21808,7 @@
       </c>
       <c r="E971" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、粤菜、咸、鲜美、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -21772,7 +22092,11 @@
           <t>第1步：将清洗好的鲍鱼放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第2步：蒸制完成 将鲍鱼从蒸箱里取出；第3步：将黄酒 糟卤 鸡粉 盐 白糖和蒜片放入碗中混合均匀 制成糟汁 糟汁可以根据自己的喜好进行调制 不喜欢偏甜的可以减少白糖的量 觉得味道淡可以多加一些糟卤 因为糟卤是咸味的；第4步：将蒸好的鲍鱼进行处理 鲍鱼肉和壳的连接处用勺子或者不锈钢小刀划断就可以轻松取出鲍鱼肉 鲍鱼头上的牙齿要去掉 鲍鱼的内脏也要去除 不可以食用 鲍鱼肉上有一层黑色黏膜 需要清洗干净；第5步：将清洗干净的熟鲍鱼放入调好的糟汁中；第6步：用保鲜膜密封好之后 放入冰箱冷藏4到8小时使鲍鱼入味；第7步：将浸泡好入味的鲍鱼捞出盛入盘中；第8步：将葱切成细丝；第9步：将鲍鱼改刀 切成片 放入盘中；第10步：放上葱丝 点缀鱼子酱 一道简单又高级的菜肴就做好了</t>
         </is>
       </c>
-      <c r="E984" s="16" t="n"/>
+      <c r="E984" s="16" t="inlineStr">
+        <is>
+          <t>晚餐、地方风味、酒香、鲜美、清淡、老人</t>
+        </is>
+      </c>
     </row>
     <row r="985" ht="48" customHeight="1" s="10">
       <c r="B985" s="13" t="inlineStr">
@@ -21790,7 +22114,11 @@
           <t>第1步：食材准备；第2步：将全麦面粉、鸡蛋、酸奶、蜂蜜、酵母粉、抹茶粉混合揉成面团，面团覆盖上保鲜膜，室温发酵1小时；第3步：紫薯去皮切块装入碗中，放入方太CSCD42-F1蒸箱，选择普通蒸模式，100度，蒸20分钟；第4步：蒸熟的紫薯加牛奶捣烂成紫薯泥，然后搓成乒乓球大小的内馅球备用；第5步：1小时后，取出面团，捏成手掌心大小的圆饼，将紫薯球包进去封口。用虎口调整形状，按压成小圆饼；第6步：方太燃气灶小火3档，无需放油，加入圆饼煎烙到两面金黄；第7步：5分钟后，取下锅盖，饼完全熟透，取出装盘撒上少许椰蓉，即可食用；第8步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E985" s="14" t="n"/>
+      <c r="E985" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、甜、减脂、便秘、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="986" ht="48" customHeight="1" s="10">
       <c r="B986" s="15" t="inlineStr">
@@ -22488,7 +22816,7 @@
       </c>
       <c r="E1017" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、地方风味、咸、儿童、烤制类</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22924,11 @@
           <t>第1步：将秋葵洗净，切掉头部和尾部，去籽备用；第2步：将胡萝卜和葱洗净，胡萝卜切碎末备用，葱切丝备用；第3步：将鲜虾洗净，去除虾线，切掉虾头，将虾壳剥掉，取出虾肉；第4步：取部分虾仁放入搅拌机内，打成泥状盛出；第5步：放入盐、淀粉、胡椒粉、胡萝卜末，搅拌均匀；第6步：将胡萝卜虾肉泥装入裱花袋中；第7步：用裱花袋将虾肉泥挤入秋葵内；第8步：将挤好虾肉泥的秋葵和剩余的虾仁分别放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第9步：蒸制完成后取出，放上蒸好的虾仁，撒上葱丝，在盘中淋上生抽，即可享用</t>
         </is>
       </c>
-      <c r="E1022" s="16" t="n"/>
+      <c r="E1022" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、清淡、鲜美、减脂、儿童、养胃</t>
+        </is>
+      </c>
     </row>
     <row r="1023" ht="48" customHeight="1" s="10">
       <c r="B1023" s="13" t="inlineStr">
@@ -22790,7 +23122,11 @@
           <t>第1步：将整鸭清洗干净，剁成大块。；第2步：锅中注入清水，大火煮沸，轻轻放入鸭块。；第3步：焯水约30秒后捞出，沥干备用。；第4步：虫草花需提前浸泡，使其充分吸收水分。；第5步：依次加入焯好的鸭块、泡软的虫草花、已蒸熟且口味温和的火腿与干贝，倒入清汤和黄酒。；第6步：打开方太集成烹饪中心，将盛满食材的小盅，放在烹饪机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作，一键开启智能烹饪。；第7步：待计时结束取出，撒上适量盐与味粉，提香增味。</t>
         </is>
       </c>
-      <c r="E1031" s="14" t="n"/>
+      <c r="E1031" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、酒香、清淡、鲜美、老人、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1032" ht="48" customHeight="1" s="10">
       <c r="B1032" s="15" t="inlineStr">
@@ -22918,7 +23254,11 @@
           <t>第1步：羊肋排斩成块，用水洗净，去除羊肉中的血水，鲜当归切段。；第2步：放入锅中，加入清水，焯水后洗净浮沫。；第3步：将羊肋排、鲜当归、红枣，放入汤碗中，加入清水，盖保鲜膜。；第4步：打开方太智能烹饪设备，将蒸烤架放入蒸箱第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。；第5步：取出后加入盐调味，撒入枸杞和养心菜。</t>
         </is>
       </c>
-      <c r="E1037" s="14" t="n"/>
+      <c r="E1037" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、地方风味、清淡、养胃、贫血、哺乳</t>
+        </is>
+      </c>
     </row>
     <row r="1038" ht="48" customHeight="1" s="10">
       <c r="B1038" s="15" t="inlineStr">
@@ -22936,7 +23276,11 @@
           <t>第1步：将蔓越莓干和去核红枣干切碎备用。；第2步：将红糖和牛奶混匀，搅拌至无明显颗粒。；第3步：将糯米粉、红豆粉、薏仁粉、红糖牛奶液和玉米油混合并揉成光滑团状。；第4步：再加入果干类揉搓均匀。；第5步：取一个月饼模具，将粉团分成35g一个，按压成喜欢的形状，并均匀摆在垫有有空硅胶垫的蒸烤架上。；第6步：打开蒸烤箱，将蒸烤架放入第二层，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1038" s="16" t="n"/>
+      <c r="E1038" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、中式面点、甜、儿童、老人、便秘</t>
+        </is>
+      </c>
     </row>
     <row r="1039" ht="48" customHeight="1" s="10">
       <c r="B1039" s="13" t="inlineStr">
@@ -23064,7 +23408,11 @@
           <t>第1步：将30g芝麻油淋到鸡身，均匀涂抹，用油纸包裹住整个鸡身。；第2步：锅中倒入部分粗盐铺平底部，将包裹好的鸡放进去，再倒入剩余的粗盐，直至掩盖过鸡肉，盖上锅盖，设置：60分钟/9档。</t>
         </is>
       </c>
-      <c r="E1044" s="16" t="n"/>
+      <c r="E1044" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、粤菜、咸、咸香、鲜美、老人、儿童、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1045" ht="48" customHeight="1" s="10">
       <c r="B1045" s="13" t="inlineStr">
@@ -23128,7 +23476,7 @@
       </c>
       <c r="E1047" s="14" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>晚餐、西餐风味、咸、香、上班族、耗时长</t>
         </is>
       </c>
     </row>
@@ -23216,7 +23564,7 @@
       </c>
       <c r="E1051" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>下午茶、甜、地方风味、老人、儿童、养胃、烤制类</t>
         </is>
       </c>
     </row>
@@ -23302,7 +23650,11 @@
           <t>第1步：苹果切片、梨切片，与调料和肉抓匀，密封腌制2小时；；第2步：将饼皮两边卡在烤架上，成拱起状；；第3步：将五花肉片平铺在铺了硅油纸的烤盘上；；第4步：打开方太智能烹饪设备，将蒸烤盘放入第4层，蒸烤架放入第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1055" s="14" t="n"/>
+      <c r="E1055" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、西餐风味、咸、甜、辣、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="1056" ht="48" customHeight="1" s="10">
       <c r="B1056" s="15" t="inlineStr">
@@ -23386,7 +23738,11 @@
           <t>第1步：食材准备；第2步：红薯切丁；第3步：放入方太C2.i智能蒸箱，设置普通蒸模式，100度，蒸15分钟；第4步：红薯晾凉后，倒入大碗中捣成泥，越细腻越好；第5步：红薯泥中加入煮好的小米粥；第6步：加入低筋面粉、糖、酵母；第7步：将所有材料搅拌成絮状，加入面粉（面粉的量需要酌情考虑，揉面时觉得稀了就再加一点点低筋面粉）。揉成光滑面团。放入保鲜袋，面团静置10分钟；第8步：发酵完成后，拿出来再揉一下，擀成约1厘米厚的薄饼；第9步：先用刀切成长条，再切成小三角形；第10步：盖上保鲜膜，发酵30分钟；第11步：方太CS34BW磁控电磁灶开至3段小火，热锅融化黄油，放入红薯小米面包煎制；第12步：小火煎至金黄，翻面，煎至两面金黄即可；第13步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E1059" s="14" t="n"/>
+      <c r="E1059" s="14" t="inlineStr">
+        <is>
+          <t>早餐、中式面点、甜、儿童、老人、养胃、便秘</t>
+        </is>
+      </c>
     </row>
     <row r="1060" ht="48" customHeight="1" s="10">
       <c r="B1060" s="15" t="inlineStr">
@@ -23976,7 +24332,11 @@
           <t>第1步：梭子蟹洗净，除去内脏，切件沥干放入盘子中。取一小碗加入苏梅酱、豆豉、柠檬汁、红椒丝、姜丝、蒜末和食用油，混匀后淋在梭子蟹上，再放至复式蒸锅备用。；第2步：主锅中加入水，盖上锅盖，放上复式蒸锅，设置：23分钟/140℃/1档蒸煮。烹饪结束，撒上葱花趁热食用。</t>
         </is>
       </c>
-      <c r="E1086" s="16" t="n"/>
+      <c r="E1086" s="16" t="inlineStr">
+        <is>
+          <t>晚餐、江浙菜、酸、甜、鲜美、海鲜风味</t>
+        </is>
+      </c>
     </row>
     <row r="1087" ht="48" customHeight="1" s="10">
       <c r="B1087" s="13" t="inlineStr">
@@ -24324,7 +24684,11 @@
           <t>第1步：将芒果削皮切小丁备用。；第2步：取1大碗，放入钵仔糕粉、温水和白砂糖混合均匀。；第3步：蒸烤架摆上小碗，将黄油融化后在小碗内壁薄薄的刷一层。；第4步：倒入钵仔糕粉浆，每个40克左右，七分满。开启电源，取出水箱加满水，将蒸烤架放入烹饪机，选择【开始烹饪】按键，按屏幕提示操作即可</t>
         </is>
       </c>
-      <c r="E1102" s="16" t="n"/>
+      <c r="E1102" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、地方风味、甜、甜点、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1103" ht="48" customHeight="1" s="10">
       <c r="B1103" s="13" t="inlineStr">
@@ -24496,7 +24860,11 @@
           <t>第1步：食材准备；第2步：1.百合扒开清洗干净；第3步：热锅倒油，放入肉糜炒至干香；第4步：3.加入蟹味菇和黑鸡枞炒软；第5步：加入蚝油和豆瓣酱炒出香味；第6步：加入水煮两分钟，倒出备用；第7步：百合均匀铺在烤盘上，均匀地淋上肉酱，撒上枸杞；第8步：将烤盘放进蒸烤烹饪机；第9步：设置普通蒸模式，100℃，10分钟；第10步：烹饪完成，取出烤盘，撒上葱花 ，淋上热油即可享有</t>
         </is>
       </c>
-      <c r="E1110" s="16" t="n"/>
+      <c r="E1110" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、地方风味、咸、微辣、鲜美、养胃、更年期</t>
+        </is>
+      </c>
     </row>
     <row r="1111" ht="48" customHeight="1" s="10">
       <c r="B1111" s="13" t="inlineStr">
@@ -24558,7 +24926,11 @@
           <t>第1步：将南瓜切小丁备用；大米、小米清洗干净备用。；第2步：将南瓜丁、大米、小米和水，放入砂锅中。；第3步：将砂锅放在蒸烤架上，置于机器中间层，设置普通蒸100℃，70分钟。</t>
         </is>
       </c>
-      <c r="E1113" s="14" t="n"/>
+      <c r="E1113" s="14" t="inlineStr">
+        <is>
+          <t>早餐、清淡、甜、儿童、老人、养胃、便秘、助眠</t>
+        </is>
+      </c>
     </row>
     <row r="1114" ht="48" customHeight="1" s="10">
       <c r="B1114" s="15" t="inlineStr">
@@ -24798,7 +25170,7 @@
       </c>
       <c r="E1124" s="16" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、圣诞节、西餐风味、咸、香、儿童、烤制类</t>
         </is>
       </c>
     </row>
@@ -24886,7 +25258,7 @@
       </c>
       <c r="E1128" s="16" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>晚餐、西餐风味、咸、上班族、更年期、耗时长</t>
         </is>
       </c>
     </row>
@@ -24906,7 +25278,11 @@
           <t>第1步：糯米鸡无需解冻，取出糯米鸡，放在蒸烤架上；第2步：打开方太智能烹饪设备，将水箱加满水，蒸烤架放入设备中间层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1129" s="14" t="n"/>
+      <c r="E1129" s="14" t="inlineStr">
+        <is>
+          <t>早餐、午餐、粤菜、咸、上班族、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1130" ht="48" customHeight="1" s="10">
       <c r="B1130" s="15" t="inlineStr">
@@ -25210,7 +25586,11 @@
           <t>第1步：食材准备；第2步：碗中放入带子，加上一根百里香，撒盐、黑胡椒粉、柠檬汁，抓拌均匀，腌制十分钟；第3步：吐司去边，切成两份；第4步：方太蒸烤烹饪机，设置上下火模式，150℃，10分钟开始预热；第5步：吐司放在烤盘上；第6步：放上腌制好的带子；第7步：最后撒点马苏里拉芝士；第8步：预热完成，放入方太蒸烤烹饪机第二层；第9步：点缀上明太鱼籽即可；第10步：尽情享受</t>
         </is>
       </c>
-      <c r="E1143" s="14" t="n"/>
+      <c r="E1143" s="14" t="inlineStr">
+        <is>
+          <t>晚餐、西餐风味、奶香、咸、鲜美、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="1144" ht="48" customHeight="1" s="10">
       <c r="B1144" s="15" t="inlineStr">
@@ -25404,7 +25784,11 @@
           <t>第1步：食材准备；第2步：鳕鱼洗净，去刺，用料理棒打成泥，加入淀粉、盐、蛋液搅拌均匀；第3步：用锡纸卷起；第4步：放入方太蒸箱，设置普通蒸模式，100度，蒸20分钟，剥开锡纸即可；第5步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E1152" s="16" t="n"/>
+      <c r="E1152" s="16" t="inlineStr">
+        <is>
+          <t>早餐、儿童、清淡、养胃</t>
+        </is>
+      </c>
     </row>
     <row r="1153" ht="48" customHeight="1" s="10">
       <c r="B1153" s="13" t="inlineStr">
@@ -25710,7 +26094,7 @@
       </c>
       <c r="E1166" s="16" t="inlineStr">
         <is>
-          <t>汤类</t>
+          <t>午餐、晚餐、粤菜、清淡、甜、老人、儿童、养胃、助眠、汤类</t>
         </is>
       </c>
     </row>
@@ -25796,7 +26180,11 @@
           <t>第1步：主锅中加入食用油和蒜蓉，盖上锅盖，设置：1分钟/大火/热炒。；第2步：加入西兰花、盐、蚝油和水，盖上锅盖，设置：3分钟/猛火/热炒。</t>
         </is>
       </c>
-      <c r="E1170" s="16" t="n"/>
+      <c r="E1170" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、清淡、减脂、便秘、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1171" ht="48" customHeight="1" s="10">
       <c r="B1171" s="13" t="inlineStr">
@@ -25836,7 +26224,11 @@
           <t>第1步：将冻的半硬的猪五花切成5x5mm的小丁。；第2步：在切好的肉中加入盐 ，白胡椒粉，生抽和鸡粉，再加入葱姜汁和蛋清，搅打上劲后静置1小时备用。；第3步：白萝卜去皮，修整成圆球，在用挖球器把萝卜球挖空心，留表皮5mm左右厚度。；第4步：把肉酿入萝卜中。；第5步：再把酿好的萝卜狮子头放入大碗中，加入鸡汤，放在蒸烤架上。；第6步：打开蒸烤一体机，将烤架放在蒸烤一体机第 2层，开启电源，选择”开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1172" s="16" t="n"/>
+      <c r="E1172" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、清淡、鲜美、儿童、老人、养胃、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1173" ht="48" customHeight="1" s="10">
       <c r="B1173" s="13" t="inlineStr">
@@ -25898,7 +26290,11 @@
           <t>第1步：将澄面倒入碗中，加入开水将澄面烫熟，用筷子搅拌均匀。；第2步：加入糯米粉、青麦汁继续搅拌，用手揉成面团备用。；第3步：荠菜放入锅中焯水后捞出，将烫好的荠菜切碎。；第4步：将肉糜放入碗中，加入盐、鸡粉、生抽、胡椒粉、麻油拌上劲，放入荠菜，搅拌均匀。；第5步：用手将拌好的荠菜肉馅搓成40克1个的小丸子。；第6步：将揉好的面团擀成圆饼状。；第7步：将荠菜丸子包入擀好的面皮中，搓成圆团状。；第8步：开启电源，将青团放入设备第2层，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1175" s="14" t="n"/>
+      <c r="E1175" s="14" t="inlineStr">
+        <is>
+          <t>清明节、早餐、中式面点、咸</t>
+        </is>
+      </c>
     </row>
     <row r="1176" ht="48" customHeight="1" s="10">
       <c r="B1176" s="15" t="inlineStr">
@@ -26336,7 +26732,7 @@
       </c>
       <c r="E1195" s="14" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>晚餐、西餐风味、咸、酒香、上班族、更年期、耗时长</t>
         </is>
       </c>
     </row>
@@ -26510,7 +26906,11 @@
           <t>第1步：将红糖馒头放入蒸烤架上。开启电源，取出水箱加满水，将蒸烤架放入烹饪机中间层，选择【开始烹饪】按键，按屏幕提示操作即可</t>
         </is>
       </c>
-      <c r="E1203" s="14" t="n"/>
+      <c r="E1203" s="14" t="inlineStr">
+        <is>
+          <t>早餐、中式面点、甜、儿童、老人、养胃、贫血</t>
+        </is>
+      </c>
     </row>
     <row r="1204" ht="48" customHeight="1" s="10">
       <c r="B1204" s="15" t="inlineStr">
@@ -26858,7 +27258,11 @@
           <t>第1步：洗净的鳝鱼开花刀 加入葱段，姜片，10g黄酒和盐。腌制10分钟备用。；第2步：火腿切成丝备用。；第3步：取一锅，加入150g酒酿 、50g黄酒、糟卤、蒸鱼豉油、白砂糖和水搅拌均匀，开火，煮开后小火煮5分钟。；第4步：过滤备用。；第5步：把鳝鱼放入盘中，表面再放50g酒酿和火腿丝，再淋上蒸鱼汁放在蒸烤盘上备用。；第6步：打开蒸烤一体机，将蒸烤盘放在蒸烤一体机第 2层，开启电源，选择”开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1219" s="14" t="n"/>
+      <c r="E1219" s="14" t="inlineStr">
+        <is>
+          <t>晚餐、江浙菜、酒香、鲜美、养胃、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1220" ht="48" customHeight="1" s="10">
       <c r="B1220" s="15" t="inlineStr">
@@ -27318,7 +27722,7 @@
       </c>
       <c r="E1240" s="16" t="inlineStr">
         <is>
-          <t>汤类</t>
+          <t>午餐、晚餐、清淡、鲜美、老人、哺乳、更年期、养胃、汤类</t>
         </is>
       </c>
     </row>
@@ -27536,7 +27940,11 @@
           <t>第1步：食材准备；第2步：大盆中加入面粉，倒入温水，再加入酵母粉、糖、玉米油，用筷子搅拌成絮状，再用手揉成表面光滑的面团；第3步：取出两个小面团，一个加入红曲粉，作为红色面团，一个加入竹炭粉，揉成黑色面团；第4步：面团揉好后的样子；第5步：将剩余的白面团平均分成6份，滚圆；第6步：红色面团擀薄片，用剪刀分别切出若干大圆和小圆来；第7步：照图中的样子将红色圆片粘到面团上面，用黑色面团做出眉毛，嘴巴，眼睛来，发酵至1.5倍大小；第8步：放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第9步：尽情享用吧</t>
         </is>
       </c>
-      <c r="E1250" s="16" t="n"/>
+      <c r="E1250" s="16" t="inlineStr">
+        <is>
+          <t>早餐、中式面点、甜、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1251" ht="48" customHeight="1" s="10">
       <c r="B1251" s="13" t="inlineStr">
@@ -27774,7 +28182,11 @@
           <t>第1步：将黄油融化，加入蛋液和纯牛奶搅拌均匀；第2步：将麻薯预拌粉、四神粉和芝士粉加入液体中，用打蛋器搅拌均匀成面糊状；第3步：将面糊装入裱花袋，裱花袋剪一个0.7cm左右小孔，烤盘铺油纸，把裱花袋中面糊挤入烤盘成10cm左右的长条形；第4步：打开蒸烤箱，按屏幕提示操作。烹饪结束后放凉即可食用，剩余的装入自封袋或塑料密封罐，放在阴凉避光处保存，易吸潮，尽快食用</t>
         </is>
       </c>
-      <c r="E1261" s="14" t="n"/>
+      <c r="E1261" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、甜、儿童、老人、养胃、便秘</t>
+        </is>
+      </c>
     </row>
     <row r="1262" ht="48" customHeight="1" s="10">
       <c r="B1262" s="15" t="inlineStr">
@@ -28080,7 +28492,7 @@
       </c>
       <c r="E1275" s="14" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>下午茶、甜、老人、更年期、养胃、助眠、耗时长</t>
         </is>
       </c>
     </row>
@@ -28210,7 +28622,11 @@
           <t>第1步：主锅中加入1000g猪蹄块、20g姜片、30g料酒和1000g水，盖上锅盖，设置：10分钟/大火/红烧。；第2步：主锅中加入食用油、白糖、姜片和大葱片，盖上锅盖，设置：3分钟/猛火/热炒。；第3步：加入焯好的猪蹄块，盖上锅盖，设置：2分钟/猛火/热炒。；第4步：主锅中加入郫县豆瓣酱、风味豆豉、干辣椒、花椒、生抽、红烧汁、老抽和1100g水，盖上锅盖，设置：70分钟/中火/红烧。</t>
         </is>
       </c>
-      <c r="E1281" s="14" t="n"/>
+      <c r="E1281" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、川湘菜、辣、咸、香、哺乳、贫血、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1282" ht="48" customHeight="1" s="10">
       <c r="B1282" s="15" t="inlineStr">
@@ -28340,7 +28756,7 @@
       </c>
       <c r="E1287" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、西餐风味、咸、鲜美、减脂、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -28558,7 +28974,11 @@
           <t>第1步：将冷冻虾饺放在垫有油纸的蒸架上，放入蒸烤一体机第2层，水箱加满水，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1297" s="14" t="n"/>
+      <c r="E1297" s="14" t="inlineStr">
+        <is>
+          <t>早餐、粤菜、中式面点、清淡、鲜美、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1298" ht="48" customHeight="1" s="10">
       <c r="B1298" s="15" t="inlineStr">
@@ -28621,7 +29041,11 @@
           <t>第1步：食材准备；第2步：小米提前浸泡一个小时；第3步：牛肉切碎，小葱切段；第4步：加生抽、料酒、盐、五香粉、辣椒粉用手按摩牛肉帮助配料入味，腌制30分钟；第5步：小米滤水沥干，同腌制的牛肉均匀的抓到一起；第6步：平铺入盘中；第7步：放入方太C2.i智能蒸箱，设置普通蒸模式，100度，蒸40分钟；第8步：取出撒上葱花即可；第9步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E1300" s="16" t="n"/>
+      <c r="E1300" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、地方风味、咸、养胃、老人、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1301" ht="48" customHeight="1" s="10">
       <c r="B1301" s="13" t="inlineStr">
@@ -28839,7 +29263,7 @@
       </c>
       <c r="E1310" s="16" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、粤菜、海鲜风味、咸、鲜美、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -29101,7 +29525,11 @@
           <t>第1步：鳝鱼背洗净。；第2步：烧一锅水，把鳝鱼背放入锅中焯10秒马上捞出。；第3步：捞出的鳝鱼背放入清水中把稀出的粘液清理干净。；第4步：取小锅，把黄酒、冰糖和盐一起倒入。；第5步：煮沸后倒入小碗里，备用。；第6步：取一盘，放入鳝鱼背和青豆瓣。；第7步：再把制作好的黄酒倒入盘中撒上姜丝和一半的洋魁花。；第8步：打开蒸烤一体机，将蒸烤架放入蒸烤一体机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1322" s="16" t="n"/>
+      <c r="E1322" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、酒香、鲜美、老人、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1323" ht="48" customHeight="1" s="10">
       <c r="B1323" s="13" t="inlineStr">
@@ -29295,7 +29723,11 @@
           <t>第1步：食材准备；第2步：方太燃气灶开大火7档，锅内放水，烧开后将娃娃菜烫到8分熟，捞出来过凉水，攥干水待用；第3步：西红柿去皮，切细丁待用；虾仁剁成虾泥，放白胡椒、部分盐、米酒拌匀，腌制一会；第4步：山药去皮，切小段，打成泥，山药泥中加入玉米粒、虾泥、香油一起搅拌均匀，拌好的馅料放在一片娃娃菜梗位置，然后用菜叶卷起来后用牙签固定；第5步：娃娃菜卷做好之后，将蒸盘放入方太F1蒸箱中，选择普通蒸模式（默认温度100度）15分钟即可；第6步：开中火5档，锅内加入蒜蓉炒香后加入番茄丁，加少许盐调味，再加一点水炖煮一下，加入黑胡椒，煮到番茄软烂，大火收汁至浓稠；第7步：娃娃菜卷蒸好以后，在娃娃菜卷周围淋上一圈番茄汤汁即可食用；第8步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E1331" s="14" t="n"/>
+      <c r="E1331" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、清淡、鲜美、儿童、老人、减脂</t>
+        </is>
+      </c>
     </row>
     <row r="1332" ht="48" customHeight="1" s="10">
       <c r="B1332" s="15" t="inlineStr">
@@ -29335,7 +29767,11 @@
           <t>第1步：双椒鳙鱼头：将1个鳙鱼头去除鱼鳞、鱼鳃和内脏，洗净并沥干水分，再沿着背鳍将鱼头对半劈开，鱼背肉厚处片刀。；第2步：将15g葱段、6g姜片放在鱼盘底部，放入鳙鱼头，将2.5g盐均匀抹在鱼头上，倒入30g料酒，腌制10分钟。；第3步：将鱼头放入大号双耳盘中，将200g双色剁椒酱浇在鳙鱼头上。；第4步：腊味合蒸：处理食材，腊肉和香肠切成薄片，咸鱼切块，铺在小号碗中。；第5步：豆豉蒸香干：200g香干切片，加入400g温水、2g盐浸泡30min。；第6步：取出豆干铺在小号碗中，加入30g红剁椒、10g蒜末、6g豆豉、7g猪油、2g白砂糖、6g生抽、1g老抽、25g纯净水，准备烹饪。；第7步：酱醋茄子：将350g茄子洗净去蒂，切成7cm段，摆放在中号碗中。；第8步：取一小碗准备酱料：12g蒜末、15香醋、30g生抽、1g盐、5g白砂糖混合均匀备用。；第9步：红枣南瓜：400g南瓜去皮去瓜瓤，10个红枣去核，清洗干净。；第10步：将南瓜切成小块、红枣对半切开，摆入中号碗中。；第11步：将5道菜放入蒸烤盘和蒸烤架上，蒸烤架放入第1层，蒸烤盘放入第3层。取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1333" s="14" t="n"/>
+      <c r="E1333" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、川湘菜、辣、咸、上班族、老人</t>
+        </is>
+      </c>
     </row>
     <row r="1334" ht="48" customHeight="1" s="10">
       <c r="B1334" s="15" t="inlineStr">
@@ -29397,7 +29833,11 @@
           <t>第1步：将根玉米剥皮剁小段；第2步：将玉米段装入盘中，放置在蒸烤架上放入烹饪机中间层，选择【开始烹饪】按键，按屏幕提示操作即可</t>
         </is>
       </c>
-      <c r="E1336" s="16" t="n"/>
+      <c r="E1336" s="16" t="inlineStr">
+        <is>
+          <t>早餐、下午茶、甜、清淡、儿童、老人、便秘</t>
+        </is>
+      </c>
     </row>
     <row r="1337" ht="48" customHeight="1" s="10">
       <c r="B1337" s="13" t="inlineStr">
@@ -30825,7 +31265,7 @@
       </c>
       <c r="E1401" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、川湘菜、辣、香辣、咸、上班族、减脂、烤制类</t>
         </is>
       </c>
     </row>
@@ -30845,7 +31285,11 @@
           <t>第1步：豆腐切小丁，胡萝卜和泡发后的黑木耳切丝，韭菜切碎。；第2步：取一炒锅，倒入15g食用油，放入豆腐丁炒制略微金黄，再加入胡萝卜丝、木耳丝一起煸炒断生，最后加入韭菜碎翻炒均匀后盛出。；第3步：炒好的馅料中加入生抽、蚝油、盐、五香粉、鸡精、香油，搅拌均匀。；第4步：将饺子皮擀薄，用水弄湿边缘，包入适量馅料，两边卷起，卷口朝下放置于蒸烤架上。；第5步：将蒸烤架置于机器中间层，设置普通蒸100℃，12分钟。</t>
         </is>
       </c>
-      <c r="E1402" s="16" t="n"/>
+      <c r="E1402" s="16" t="inlineStr">
+        <is>
+          <t>早餐、午餐、中式面点、清淡、减脂、便秘、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1403" ht="48" customHeight="1" s="10">
       <c r="B1403" s="13" t="inlineStr">
@@ -31545,7 +31989,11 @@
           <t>第1步：鲈鱼洗净。；第2步：洗净后拿出，去中骨。；第3步：鱼肉斜刀切3厘米的厚片。；第4步：放入鱼盘中备用。；第5步：蚕豆去皮后掰成两半备用。；第6步：大火热锅，转小火下入猪油粒，炒出油。；第7步：下入姜末、蒜末爆香。；第8步：再加入六月鲜豆瓣酱炒出香味。；第9步：把炒香的酱放在鲈鱼上，撒上蚕豆。；第10步：将鱼盘放在蒸架上。；第11步：打开方太智能烹饪设备，将蒸架放入蒸箱第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。；第12步：将蒸好的鱼撒上红椒粒、葱花。；第13步：浇上热油。；第14步：最后淋上蒸鱼豉油。</t>
         </is>
       </c>
-      <c r="E1434" s="16" t="n"/>
+      <c r="E1434" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、清淡、鲜美、老人、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1435" ht="48" customHeight="1" s="10">
       <c r="B1435" s="13" t="inlineStr">
@@ -31629,7 +32077,11 @@
           <t>第1步：菜心去除老根，对半切开。；第2步：将蒜片和盐1g、白糖2g、鸡精0.5g、生抽10g和蚝油3g放入碗中拌匀，备用。；第3步：中号盘中加入猪油10g和玉米油10g。；第4步：打开蒸烤一体机，将蒸烤架放在蒸烤一体机第 2层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。；第5步：将蒜片和调味汁加入到菜心中，翻拌均匀备用。；第6步：热油结束后将菜心放入中号盘中拌匀。；第7步：关门继续烹饪。</t>
         </is>
       </c>
-      <c r="E1438" s="16" t="n"/>
+      <c r="E1438" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、粤菜、清淡、蒜香、减脂、便秘、老人、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1439" ht="48" customHeight="1" s="10">
       <c r="B1439" s="13" t="inlineStr">
@@ -31933,7 +32385,11 @@
           <t>第1步：分别将原味、抹茶味、巧克力味麻薯的所有原料混合均匀，手揉约4分钟，直至面团表面光滑无颗粒感；第2步：揉捏完成后，将面团分为25g/个，揉搓折叠揉圆（揉均匀光滑，不然影响膨胀和形状）；第3步：4.	打开方太智能烹饪设备，取出水箱加满水，将蒸烤盘放入蒸烤箱第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作</t>
         </is>
       </c>
-      <c r="E1452" s="16" t="n"/>
+      <c r="E1452" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、甜、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1453" ht="48" customHeight="1" s="10">
       <c r="B1453" s="13" t="inlineStr">
@@ -31973,7 +32429,11 @@
           <t>第1步：口蘑洗净去蒂，切片。蒜切片，备用。；第2步：青菜洗净，切成菜梗和菜叶两部分。；第3步：将口蘑片和菜梗放入中号盘中，加入10g玉米油，2g盐，生抽3g拌匀。；第4步：中号盘放在蒸烤架上，放入机器第二层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。；第5步：菜叶中加入玉米油5g，白糖1g，蒜片，鸡精0.5g，蚝油3g，拌匀。；第6步：口蘑和菜梗烹饪10min后，加入菜叶，拌匀，继续烹饪2min。</t>
         </is>
       </c>
-      <c r="E1454" s="16" t="n"/>
+      <c r="E1454" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、清淡、减脂、便秘、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="1455" ht="48" customHeight="1" s="10">
       <c r="B1455" s="13" t="inlineStr">
@@ -32233,7 +32693,11 @@
           <t>第1步：将腌制好的鸡放入大号双耳盘中铺开，并将鸡翅用锡纸包裹好。；第2步：取沥干的排骨，加入2g盐、3g白糖、5g蒜泥、1g五香粉、3g孜然粉、3g辣椒粉、10g食用油、10g料酒、10g生抽、10g蚝油和2g老抽，抓拌均匀放入盘中，放冰箱腌制2小时备用。；第3步：将腌制好的排骨均匀码放在中号碗中。；第4步：将处理好的小龙虾放入中号碗中，摆上30g姜片、20g小葱段，淋入50g啤酒。；第5步：将100g土豆丝、100g胡萝卜丝、50g茼蒿叶与20g米粉、3g盐、3g十三香粉充分混合均匀，放入小号碗中。；第6步：将200g大米洗净沥干放入小号碗中，再加入240g水，使米水充分混合均匀。；第7步：将奥尔良烤鸡和香烤排骨置于蒸烤盘上放入机器第4层，蒸米饭置于蒸烤架上放入第1层。取出水箱加满水，在设备/APP端找到并进入“亲朋欢聚套餐”，选择“开始烹饪”按键，按屏幕提示操作。当时间还剩15min时，将粉蒸三丝和清蒸小龙虾放入机器第1层的烤架上并关门</t>
         </is>
       </c>
-      <c r="E1466" s="16" t="n"/>
+      <c r="E1466" s="16" t="inlineStr">
+        <is>
+          <t>晚餐、川湘菜、辣、香辣、咸、鲜美、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="1467" ht="48" customHeight="1" s="10">
       <c r="B1467" s="13" t="inlineStr">
@@ -32361,7 +32825,11 @@
           <t>第1步：食材准备；第2步：用流动水冲洗大肠，直到大肠上的污物洗净后；第3步：锅烧热，高温反复三次炝大肠，去除大肠上的腥味；第4步：碗里放入肥肠，调入盐、糖、生抽、老抽、香叶，姜片，葱段；第5步：再倒入白酒、八角、桂皮腌制；第6步：方太蒸箱调至110℃，选择过温蒸的模式；第7步：肥肠放入蒸箱中蒸70分钟；第8步：姜切末、葱切花，蒜切末；第9步：取出蒸软的大肠，待凉后切小段备用，肥肠加少许淀粉裹匀；第10步：锅中放油，大火油炸肥肠至金黄色微焦后，捞出；第11步：锅中放底油，放入花椒，蒜末，麻辣酱，辣椒炒香；第12步：再放入糖、料酒、酱油调味翻炒一会儿；第13步：翻炒至辣椒有一点点变色后倒入先前盛出的大肠继续翻炒一小会；第14步：再放入芝麻、葱花，小炒一会儿；第15步：关火盛出装盘即可</t>
         </is>
       </c>
-      <c r="E1472" s="16" t="n"/>
+      <c r="E1472" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、川湘菜、辣、香辣、咸、上班族、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1473" ht="48" customHeight="1" s="10">
       <c r="B1473" s="13" t="inlineStr">
@@ -32579,7 +33047,7 @@
       </c>
       <c r="E1482" s="16" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、西餐风味、咸、鲜美、奶香、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -32753,7 +33221,11 @@
           <t>第1步：取一料理盆，依次称取750g鸡肉块、5g盐、10g蚝油、5g白糖、5g鸡精、20g生粉，搅拌均匀，腌制15分钟；备用。；第2步：海豚微压锅中加入食用油、红葱头、大蒜和姜块，设置：4分钟/一键大火，进行煸炒爆香。；第3步：将腌好的鸡肉平铺锅内，盖上锅盖并关闭气阀，设置：20分钟/无水焖。</t>
         </is>
       </c>
-      <c r="E1490" s="16" t="n"/>
+      <c r="E1490" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、粤菜、咸、咸香、香、上班族、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1491" ht="48" customHeight="1" s="10">
       <c r="B1491" s="13" t="inlineStr">
@@ -33035,7 +33507,11 @@
           <t>第1步：锅中加入30g橄榄油、80g红葱头、50g姜粒、50g蒜粒、30g芹菜粒和8个小番茄，设置：3分钟/一键大火，期间不停翻炒。；第2步：将腌制好的鱼块均匀铺入锅中，加上6个橄榄，盖上锅盖，设置：12分钟/无水焖。</t>
         </is>
       </c>
-      <c r="E1503" s="14" t="n"/>
+      <c r="E1503" s="14" t="inlineStr">
+        <is>
+          <t>晚餐、西餐风味、咸、鲜美、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="1504" ht="48" customHeight="1" s="10">
       <c r="B1504" s="15" t="inlineStr">
@@ -33339,7 +33815,11 @@
           <t>第1步：准备杂粮米饭：三色糙米洗净，沥干水分。；第2步：将糙米放入碗中倒入水备用。；第3步：准备肉饼蒸蛋：肉末放入碗中，加入除鸡蛋外的所有食材，按顺时针方向搅打上劲。；第4步：把搅拌好的肉末分成两份，放入两个盅里 ，用手按一个凹槽，再各打入一个鸡蛋备用。；第5步：准备玉米排骨汤：排骨洗干净、玉米切长条，放入盅内，再加入盐、姜片、葱结、料酒和水备用。；第6步：准备蒜泥蒸茄子：茄子洗净，切成5厘米的长条，放入盘中，在茄子上铺上蒜泥、小米椒碎和葱花备用。；第7步：准备蟹味菇蒸鸡胸肉：蟹味菇去根，鸡胸切3厘米大小的块。；第8步：在鸡胸里加入淀粉、蒜末、姜末、生抽、料酒、盐和食用油，按顺时针方向搅拌，直至鸡肉把液体吸收。；第9步：将蟹味菇铺在盘底，再放上鸡肉，将盘子和之前准备好的食材放入蒸烤盘中。；第10步：将5道菜放入机器中，点击“开始烹饪”按键，开始烹饪。</t>
         </is>
       </c>
-      <c r="E1517" s="14" t="n"/>
+      <c r="E1517" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">午餐、晚餐、清淡、咸、上班族、老人、咸鲜、养胃、健胃消食 | </t>
+        </is>
+      </c>
     </row>
     <row r="1518" ht="48" customHeight="1" s="10">
       <c r="B1518" s="15" t="inlineStr">
@@ -33357,7 +33837,11 @@
           <t>第1步：食材准备；第2步：鸡肉切成丁状，香菇、胡萝卜切成小颗粒；第3步：方太CS34BW磁控电磁灶开至9段大火，烧开水，加入少量盐，放入白菜，烫软捞出；第4步：将鸡肉、香菇、胡萝卜放入碗中，加入姜、酒、盐、生抽、黑、白胡椒粉、糖一同腌制15分钟左右备用；第5步：白菜烫完趁热铺平案板上，将腌制好的料放在白菜上；第6步：卷起成长条；第7步：放入方太C2.i智能蒸箱，设置普通蒸模式，100度，蒸20分钟；第8步：取出撒上葱花即可；第9步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E1518" s="16" t="n"/>
+      <c r="E1518" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、清淡、减脂、儿童、老人</t>
+        </is>
+      </c>
     </row>
     <row r="1519" ht="48" customHeight="1" s="10">
       <c r="B1519" s="13" t="inlineStr">
@@ -33596,7 +34080,11 @@
           <t>第1步：将燕麦米、大米和干桑葚放入砂锅中，加入500g水。；第2步：将砂锅放在蒸烤架上，放入机器最下层，设置健康煲汤，70分钟。</t>
         </is>
       </c>
-      <c r="E1529" s="14" t="n"/>
+      <c r="E1529" s="14" t="inlineStr">
+        <is>
+          <t>早餐、甜、老人、儿童、养胃、助眠、便秘、贫血</t>
+        </is>
+      </c>
     </row>
     <row r="1530" ht="48" customHeight="1" s="10">
       <c r="B1530" s="15" t="inlineStr">
@@ -33658,7 +34146,11 @@
           <t>第1步：将冷冻芝士榴莲盒撕开盖，放在烤盘上，将烤盘放入蒸烤一体机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1532" s="16" t="n"/>
+      <c r="E1532" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、甜、甜点、儿童、更年期</t>
+        </is>
+      </c>
     </row>
     <row r="1533" ht="48" customHeight="1" s="10">
       <c r="B1533" s="13" t="inlineStr">
@@ -33764,7 +34256,11 @@
           <t>第1步：食材准备；第2步：碗中放入糯米粉、粘米粉、澄粉、南瓜泥、牛奶、玉米粉、炼乳搅拌均匀直至顺滑制成面糊备用；第3步：放入方太F1蒸箱，选择普通蒸模式，100度，蒸制20分钟，取出放凉；第4步：豆沙馅分成小剂子，约每个30克左右；第5步：面皮包入豆沙馅放入月饼模具；第6步：压出形状即可；第7步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E1537" s="14" t="n"/>
+      <c r="E1537" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、中秋、甜、甜点、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1538" ht="48" customHeight="1" s="10">
       <c r="B1538" s="15" t="inlineStr">
@@ -34024,7 +34520,11 @@
           <t>第1步：洗净的桂鱼擦干水分。；第2步：去头。；第3步：沿着骨头切开，把主骨头拿掉，鱼尾不切断。；第4步：鱼肉切花刀，先斜切至鱼皮不断。；第5步：再竖切三刀，注意不要切破鱼皮。；第6步：把鱼头和鱼肉放入碗中，加入料酒、葱段、姜片、白胡椒粉和盐，腌制20分钟。；第7步：鸡蛋打散，把腌制好的鱼肉鱼头放入蛋液中裹均匀。；第8步：面粉和生粉放入碗中混合均匀。；第9步：把裹好蛋液的鱼，均匀的沾上干粉。；第10步：将鱼放到垫有油纸的烤盘上。；第11步：打开方太智能烹饪设备，将烤盘放入蒸烤箱第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。；第12步：把番茄酱、米醋和糖放入锅中搅拌均匀。；第13步：锅中加热至浓稠后浇在鱼身上。；第14步：最后撒上青豆点缀。</t>
         </is>
       </c>
-      <c r="E1549" s="14" t="n"/>
+      <c r="E1549" s="14" t="inlineStr">
+        <is>
+          <t>晚餐、江浙菜、酸、甜、咸、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1550" ht="48" customHeight="1" s="10">
       <c r="B1550" s="15" t="inlineStr">
@@ -34219,7 +34719,11 @@
           <t>第1步：叉烧包无需解冻，取出叉烧包，放在铺有硅油纸的蒸烤架上；第2步：打开方太智能烹饪设备，将水箱加满水，蒸烤架放入设备中间层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1558" s="16" t="n"/>
+      <c r="E1558" s="16" t="inlineStr">
+        <is>
+          <t>早餐、粤菜、中式面点、甜、咸、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1559" ht="48" customHeight="1" s="10">
       <c r="B1559" s="13" t="inlineStr">
@@ -34743,7 +35247,11 @@
           <t>第1步：香蕉去皮，用料理棒打成泥状。；第2步：加入鸡蛋、牛奶、燕麦、坚果、蔓越莓干和蜂蜜，搅拌均匀。；第3步：将混合物倒入铺有锡纸的烤盘中，整成1cm高的方形燕麦糊；；第4步：将烤盘放入第二层，打开蒸烤箱，按屏幕提示操作。（手动设置：全开165℃，25分钟，不预热）</t>
         </is>
       </c>
-      <c r="E1582" s="16" t="n"/>
+      <c r="E1582" s="16" t="inlineStr">
+        <is>
+          <t>早餐、下午茶、甜、儿童、上班族、便秘</t>
+        </is>
+      </c>
     </row>
     <row r="1583" ht="48" customHeight="1" s="10">
       <c r="B1583" s="13" t="inlineStr">
@@ -34937,7 +35445,11 @@
           <t>第1步：将三文鱼肉两面煎焦黄后碾碎备用；菠菜焯水后切碎备用；鸡蛋打成蛋液备用；圣女果1切4备用。；第2步：取一个薄底披萨盘，盘底抹油，均匀地淋入蛋液，再撒上菠菜碎、三文鱼肉碎、圣女果块和罗勒碎。；第3步：打开蒸烤箱，设置全开烤180℃，10分钟。预热结束后，将三文鱼蔬菜饼放在蒸烤架上，放入机器中间层。</t>
         </is>
       </c>
-      <c r="E1591" s="14" t="n"/>
+      <c r="E1591" s="14" t="inlineStr">
+        <is>
+          <t>早餐、清淡、儿童、减脂、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="1592" ht="48" customHeight="1" s="10">
       <c r="B1592" s="15" t="inlineStr">
@@ -35593,7 +36105,11 @@
           <t>第1步：将鸡肉块放入锅中。；第2步：加入水800g、料酒20g、生姜35g，冷水煮沸后捞出，用温水洗净。；第3步：干枸杞加水浸泡至发胀后沥干水分备用。；第4步：取一铸铁锅，加入焯水鸡块、新鲜椰肉条、珍珠马蹄、NFC100%椰子水、盐、15g生姜和红枣放在蒸烤架上。；第5步：打开方太蒸烤一体机EP1，将蒸烤架放入蒸烤箱第2层，水箱加满水，开启电源，选择“开始烹饪”按键，按屏幕提示操作。；第6步：烹饪结束后，放上泡发的枸杞即可。</t>
         </is>
       </c>
-      <c r="E1621" s="14" t="n"/>
+      <c r="E1621" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、地方风味、清淡、鲜美、儿童、老人、哺乳、养胃</t>
+        </is>
+      </c>
     </row>
     <row r="1622" ht="48" customHeight="1" s="10">
       <c r="B1622" s="15" t="inlineStr">
@@ -36249,7 +36765,11 @@
           <t>第1步：食材准备；第2步：三文鱼洗净，用厨房纸擦干；第3步：蒜瓣去皮切片，百里香一半切碎；第4步：三文鱼加入食盐、料酒及百里香碎一同搅拌腌制10分钟；第5步：放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第6步：方太灶具调至8段火，热锅热油，将蒸好的三文鱼及蒜片一同放入煎制；第7步：三文鱼煎至两面金黄，撒上黑胡椒碎；第8步：盛出摆盘，淋上生抽，点缀百里香即可；第9步：美味的低温清蒸三文鱼就做好了</t>
         </is>
       </c>
-      <c r="E1651" s="14" t="n"/>
+      <c r="E1651" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、西餐风味、清淡、鲜美、减脂、儿童、上班族</t>
+        </is>
+      </c>
     </row>
     <row r="1652" ht="48" customHeight="1" s="10">
       <c r="B1652" s="15" t="inlineStr">
@@ -36445,7 +36965,7 @@
       </c>
       <c r="E1660" s="16" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>早餐、晚餐、清淡、老人、减脂、养胃、便秘、耗时长</t>
         </is>
       </c>
     </row>
@@ -37543,7 +38063,11 @@
           <t>第1步：甘薯条无需解冻，取出甘薯条，放在铺有硅油纸的蒸烤盘上；第2步：打开方太智能烹饪设备，将蒸烤盘放入设备中间层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1710" s="16" t="n"/>
+      <c r="E1710" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、甜、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1711" ht="48" customHeight="1" s="10">
       <c r="B1711" s="13" t="inlineStr">
@@ -37937,7 +38461,7 @@
       </c>
       <c r="E1728" s="16" t="inlineStr">
         <is>
-          <t>汤类</t>
+          <t>午餐、晚餐、地方风味、清淡、养胃、儿童、老人、汤类</t>
         </is>
       </c>
     </row>
@@ -37959,7 +38483,7 @@
       </c>
       <c r="E1729" s="14" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>下午茶、粤菜、甜、甜品、儿童、老人、助眠、养胃、耗时长</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38525,11 @@
           <t>第1步：山楂泡水洗净，铁棍山药去皮，切成小段，陈皮泡水备用；；第2步：将山楂、山药段、红枣、陈皮放入蒸烤盘中。；第3步：将蒸烤盘放入蒸烤箱第2层，设置100℃，25分钟，蒸至软烂。；第4步：将蒸好的山楂等食材放入料理机，加入适量清水，打成细腻泥状。；第5步：将山楂泥倒入一口不粘锅中，加入茯苓粉和麦芽糖，开中小火炒制，混合物可以抱团。；第6步：取一方形烤盘，铺烘焙纸，刷少许植物油防粘。将炒好的混合料平铺在烤盘上，用刮刀压平至约0.8-1厘米厚度，放入冰箱冷却。；第7步：待山楂糕完全冷却凝固后切成长条并放入铺有油纸的蒸烤盘上。将烤盘放入第二层，打开蒸烤箱，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1731" s="14" t="n"/>
+      <c r="E1731" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、甜、酸、儿童、老人、健胃消食、便秘</t>
+        </is>
+      </c>
     </row>
     <row r="1732" ht="48" customHeight="1" s="10">
       <c r="B1732" s="15" t="inlineStr">
@@ -38239,7 +38767,11 @@
           <t>第1步：将全部食材加入铸铁锅中，盖上锅盖。；第2步：将铸铁锅放在蒸烤架上，放在最底层，设置：加湿烤、180℃、90min。</t>
         </is>
       </c>
-      <c r="E1742" s="16" t="n"/>
+      <c r="E1742" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、五香、酱香、咸、老人、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1743" ht="48" customHeight="1" s="10">
       <c r="B1743" s="13" t="inlineStr">
@@ -38433,7 +38965,11 @@
           <t>第1步：将食材洗净沥干放入砂锅中，并加入水。；第2步：将砂锅放在蒸烤架上，置于机器中间层，设置普通蒸100℃，60分钟。</t>
         </is>
       </c>
-      <c r="E1751" s="14" t="n"/>
+      <c r="E1751" s="14" t="inlineStr">
+        <is>
+          <t>早餐、甜、老人、儿童、贫血、助眠、养胃</t>
+        </is>
+      </c>
     </row>
     <row r="1752" ht="48" customHeight="1" s="10">
       <c r="B1752" s="15" t="inlineStr">
@@ -38495,7 +39031,11 @@
           <t>第1步：食材准备；第2步：将苋菜洗净，切成段；第3步：取蒸碗放入粉蒸粉加入盐、食用油、苋菜拌匀待用；第4步：将拌匀的米粉苋菜放入蒸碗中；第5步：放入方太蒸箱，设置普通蒸模式，100度，蒸20分钟，取出淋入芝麻油即可；第6步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E1754" s="16" t="n"/>
+      <c r="E1754" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、川湘菜、清淡、便秘、老人、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1755" ht="48" customHeight="1" s="10">
       <c r="B1755" s="13" t="inlineStr">
@@ -38601,7 +39141,11 @@
           <t>第1步：将梭子蟹洗净去壳，去除腮部，切块备用。；第2步：将粉丝放入水中泡软备用，将生姜切末，葱切丝备用。；第3步：将泡好的粉丝放入盘中，放上切好的梭子蟹，撒上姜末，盖上蟹盖。开启电源，将葱油梭子蟹放入中间层，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1759" s="14" t="n"/>
+      <c r="E1759" s="14" t="inlineStr">
+        <is>
+          <t>晚餐、江浙菜、海鲜风味、咸、鲜美</t>
+        </is>
+      </c>
     </row>
     <row r="1760" ht="48" customHeight="1" s="10">
       <c r="B1760" s="15" t="inlineStr">
@@ -38641,7 +39185,11 @@
           <t>第1步：姜切成丝备用。；第2步：草鸡切成3厘米x3厘米的块。；第3步：把草鸡放入碗中。；第4步：加入三分之一的青麦仁、姜丝、枸杞、料酒、盐、白胡椒粉和生粉。；第5步：搅拌均匀，腌制20分钟。；第6步：取一盘，把剩下的青麦仁放入盘底。；第7步：把腌制好的草鸡块放到青麦仁上。；第8步：将盘子放在蒸烤架上。；第9步：打开蒸烤一体机，将蒸烤架放入蒸烤一体机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1761" s="14" t="n"/>
+      <c r="E1761" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、地方风味、清淡、鲜美、老人、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1762" ht="48" customHeight="1" s="10">
       <c r="B1762" s="15" t="inlineStr">
@@ -38725,7 +39273,11 @@
           <t>第1步：薏米提前浸泡4小时。；第2步：咸肉切片。；第3步：冬瓜去皮去籽，切成与咸肉大小相同的大块，再切成厚5毫米的片备用。；第4步：取一锅，加入水、黄酒和咸肉。；第5步：煮开后转小火，炖煮20分钟后将咸肉捞出，留50g汤汁备用。；第6步：取一盘，把冬瓜片和咸肉片依次码放盘中。；第7步：撒上泡好的薏米，加入咸肉的汤汁、葱段和姜丝，放在蒸烤架上。；第8步：打开方太蒸烤一体机，将蒸烤架放入蒸烤一体机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。；第9步：拿出，撒上葱花。</t>
         </is>
       </c>
-      <c r="E1765" s="14" t="n"/>
+      <c r="E1765" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、清淡、咸、老人、便秘、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1766" ht="48" customHeight="1" s="10">
       <c r="B1766" s="15" t="inlineStr">
@@ -38787,7 +39339,11 @@
           <t>第1步：食材准备；第2步：千张焯水去豆腥味；第3步：猪肉糜加盐、鸡粉调味；第4步：猪肉糜放在千张上，卷起，用热水烫过的葱打结；第5步：剩余的猪肉糜倒入荠菜碎，拌匀，面筋戳一个小洞，用小勺填入猪肉荠菜末；第6步：大火将锅中水烧开，放入百叶结、面筋、小青菜和海参，煮熟即可；第7步：将锅中的食材捞出，装盅，再倒入事先煮好的鸡汤，调入少许盐；第8步：放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第9步：蒸好后拿出，放入干松茸片即可</t>
         </is>
       </c>
-      <c r="E1768" s="16" t="n"/>
+      <c r="E1768" s="16" t="inlineStr">
+        <is>
+          <t>晚餐、江浙菜、清淡、鲜美、老人、养胃、哺乳</t>
+        </is>
+      </c>
     </row>
     <row r="1769" ht="48" customHeight="1" s="10">
       <c r="B1769" s="13" t="inlineStr">
@@ -39531,7 +40087,11 @@
           <t>第1步：珍宝虾饺无需解冻，取出虾饺，放在垫有硅油纸或蒸笼布的蒸烤架上；第2步：打开方太智能烹饪设备，将水箱加满水，蒸烤架放入设备中间层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1802" s="16" t="n"/>
+      <c r="E1802" s="16" t="inlineStr">
+        <is>
+          <t>早餐、粤菜、中式面点、清淡、鲜美、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1803" ht="48" customHeight="1" s="10">
       <c r="B1803" s="13" t="inlineStr">
@@ -39681,7 +40241,11 @@
           <t>第1步：将牛排、鳕鱼表面吸干血水，分别用1g盐和黑胡椒碎腌制备用。；第2步：玉米切小段放入小号食光碗备用；将黄彩椒切小块、芦笋、小番茄洗净，用2g盐、5g味极鲜和5g橄榄油腌制备用。；第3步：取大号食光碗，将牛排、芦笋、黄彩椒、小番茄平铺，牛排两面刷上5g橄榄油。；第4步：取一个小号食光碗，将鳕鱼吸干水分放至中间。；第5步：取一个中号食光碗，将玉米和窝窝头放入。；第6步：将大号食光碗放入蒸烤盘中，中号食光碗和小号食光碗放在蒸烤架上，打开蒸烤箱，将蒸烤盘放入第4层，蒸烤架放入第1层，按屏幕提示操作。；第7步：待烹饪结束即可食用。</t>
         </is>
       </c>
-      <c r="E1809" s="14" t="n"/>
+      <c r="E1809" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、清淡、减脂、上班族、便秘</t>
+        </is>
+      </c>
     </row>
     <row r="1810" ht="48" customHeight="1" s="10">
       <c r="B1810" s="15" t="inlineStr">
@@ -39745,7 +40309,7 @@
       </c>
       <c r="E1812" s="16" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>早餐、下午茶、甜、清淡、老人、儿童、便秘、烤制类</t>
         </is>
       </c>
     </row>
@@ -40648,7 +41212,7 @@
       </c>
       <c r="E1853" s="14" t="inlineStr">
         <is>
-          <t>耗时长</t>
+          <t>晚餐、江浙菜、甜、咸、儿童、老人、耗时长</t>
         </is>
       </c>
     </row>
@@ -40890,7 +41454,7 @@
       </c>
       <c r="E1864" s="16" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>午餐、晚餐、地方风味、酸、辣、咸、上班族、减脂、烤制类</t>
         </is>
       </c>
     </row>
@@ -40910,7 +41474,11 @@
           <t>第1步：用温水将酵母、白砂糖混合活化静置3分钟后加入面粉混合均匀；；第2步：用手将面团揉至成团后静置10分钟；；第3步：将馒头面团擀开后从左至右卷起；；第4步：将面团搓成长条，切成50g/个的剂子，间隔摆在垫有油纸的蒸盘或烤架上。</t>
         </is>
       </c>
-      <c r="E1865" s="14" t="n"/>
+      <c r="E1865" s="14" t="inlineStr">
+        <is>
+          <t>早餐、中式面点、清淡</t>
+        </is>
+      </c>
     </row>
     <row r="1866" ht="48" customHeight="1" s="10">
       <c r="B1866" s="15" t="inlineStr">
@@ -41588,7 +42156,11 @@
           <t>第1步：取一锅加入水烧开，放入罗氏虾，大火烧30秒捞出备用。；第2步：取三只罗氏虾，去壳，取肉和虾膏备用。；第3步：剩下的五只罗氏虾，连壳带肉一起剁碎备用。；第4步：取一锅，锅中倒入色拉油，开小火下茄膏，炒出红油，转大火，导入罗氏虾碎。；第5步：炒出香味后加入开水，再加入盐、鸡粉和糖，保持水沸腾状态煮五分钟。；第6步：关火，过滤出虾渣、虾汤备用。；第7步：蒲菜切成长10厘米的段备用。；第8步：取一盘，在盘底铺上蒲菜，倒入虾汤。；第9步：再放上虾肉与虾膏，放到蒸烤架上。；第10步：11. 打开蒸烤一体机，将蒸烤架放在蒸烤一体机第2层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1896" s="16" t="n"/>
+      <c r="E1896" s="16" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、清淡、鲜美、老人、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1897" ht="48" customHeight="1" s="10">
       <c r="B1897" s="13" t="inlineStr">
@@ -41628,7 +42200,11 @@
           <t>第1步：南瓜去皮切片放入盘中备用。；第2步：将盘放在蒸烤架上，放入机器中间层，设置普通蒸100℃，20分钟。；第3步：结束后，取出撇掉盘中多余的水，将南瓜碾成泥，混入30g奶粉，搅拌均匀。；第4步：撒上马苏里拉芝士碎。；第5步：打开蒸烤箱，将盘放在蒸烤架上，放入机器中间层，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1898" s="16" t="n"/>
+      <c r="E1898" s="16" t="inlineStr">
+        <is>
+          <t>下午茶、西餐风味、甜、奶香、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1899" ht="48" customHeight="1" s="10">
       <c r="B1899" s="13" t="inlineStr">
@@ -41646,7 +42222,11 @@
           <t>第1步：将干山药片、茯苓、薏苡仁、百合和大枣，加纯净水浸泡10分钟。；第2步：将所有食材和水放入炖盅中，并放在蒸烤架上，放入机器中间层，设置普通蒸100℃，30分钟。</t>
         </is>
       </c>
-      <c r="E1899" s="14" t="n"/>
+      <c r="E1899" s="14" t="inlineStr">
+        <is>
+          <t>下午茶、清淡、老人、养胃、助眠、更年期</t>
+        </is>
+      </c>
     </row>
     <row r="1900" ht="48" customHeight="1" s="10">
       <c r="B1900" s="15" t="inlineStr">
@@ -41708,7 +42288,11 @@
           <t>第1步：将豆腐用刀划开，倒入锡纸盒中。；第2步：将小米辣切碎，小葱切成葱花。；第3步：取1碗，加入辣椒粉、孜然粉、五香粉、辣椒油、花椒油、芝麻油、生抽、蚝油、老干妈、蒜蓉辣椒酱、白芝麻、白砂糖、小米辣碎、葱花和纯净水，搅拌均匀。；第4步：将调制好的调料均匀地淋在豆腐上。；第5步：将锡纸盒豆腐放置在蒸烤盘中。蒸烤盘放入烹饪机中，选择选择【开始烹饪】按键，按屏幕提示操作即可。</t>
         </is>
       </c>
-      <c r="E1902" s="16" t="n"/>
+      <c r="E1902" s="16" t="inlineStr">
+        <is>
+          <t>晚餐、川湘菜、辣、香辣、咸、上班族、减脂、烤制类</t>
+        </is>
+      </c>
     </row>
     <row r="1903" ht="48" customHeight="1" s="10">
       <c r="B1903" s="13" t="inlineStr">
@@ -41770,7 +42354,11 @@
           <t>第1步：食材准备；第2步：将低筋面粉、细砂糖、植物油、酵母、菠菜汁混均匀揉成光滑的面团；第3步：将面团揉成长条分成等量的剂子；第4步：之后将剂子擀成4个圆片，依次折叠起来；第5步：然后把筷子横着放在面片中间，用力往下压；第6步：接下来折叠起来，再压一下；第7步：把面立起来；第8步：手捏住下方，用筷子在从顶部压下去；第9步：接下来发酵至1.5倍大，放入方太蒸箱，设置普通蒸模式，100度，蒸10分钟即可；第10步：尽情品尝吧</t>
         </is>
       </c>
-      <c r="E1905" s="14" t="n"/>
+      <c r="E1905" s="14" t="inlineStr">
+        <is>
+          <t>早餐、中式面点、甜、儿童、便秘</t>
+        </is>
+      </c>
     </row>
     <row r="1906" ht="48" customHeight="1" s="10">
       <c r="B1906" s="15" t="inlineStr">
@@ -41986,7 +42574,11 @@
           <t>第1步：鸡腿肉切大块，小米椒切圈，洗净沥干水分。；第2步：加入姜丝、拍蒜粒、小米辣圈、南乳汁、蚝油、糖，拌匀腌制，最后放入生粉、色拉油拌匀，抖散放入盘中。；第3步：打开蒸烤一体机，将蒸烤架放在蒸烤一体机第2层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1915" s="14" t="n"/>
+      <c r="E1915" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、粤菜、咸、咸香、儿童、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1916" ht="48" customHeight="1" s="10">
       <c r="B1916" s="15" t="inlineStr">
@@ -42114,7 +42706,11 @@
           <t>第1步：取一汤锅，放入切好的排骨、姜片和料酒，加入没过食材的清水，打开方太灶蒸烤烹饪机/方太灶具，选择大火模式烧煮。；第2步：水沸后，捞出排骨洗净备用。；第3步：取一炖盅，加入焯好的排骨、山药块、大米、茯苓粉、薏苡仁粉和纯净水。；第4步：将炖盅放在蒸烤盘中，盖上盖子，放入烹饪机中层。；第5步：取出水箱加满水，点击开始烹饪，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1921" s="14" t="n"/>
+      <c r="E1921" s="14" t="inlineStr">
+        <is>
+          <t>早餐、晚餐、清淡、养胃、老人、儿童、便秘</t>
+        </is>
+      </c>
     </row>
     <row r="1922" ht="48" customHeight="1" s="10">
       <c r="B1922" s="15" t="inlineStr">
@@ -42374,7 +42970,11 @@
           <t>第1步：将笋壳鱼洗净 改刀；第2步：放入食盐 葱 姜 料酒；第3步：腌制15分钟备用；第4步：取锅放入清水；第5步：打开方太磁控电磁灶 调至8档；第6步：水开后放入香椿；第7步：烫至香椿变绿捞出 并挤干水分；第8步：将香椿 松子 大蒜 橄榄油 食盐放入搅拌机内；第9步：制成香椿酱备用；第10步：将腌制好的笋壳鱼放入盘中；第11步：放入方太智能烹饪设备，开启电源，取出水箱加满水，选择“开始烹饪”按键，按屏幕提示操作；第12步：蒸制完成 取出鱼；第13步：将香椿酱放在鱼上；第14步：放上葱丝姜丝；第15步：淋上蒸鱼豉油；第16步：取锅放入食用油；第17步：打开方太磁控电磁灶 调至6档；第18步：油烧至7成热 淋在鱼上即可</t>
         </is>
       </c>
-      <c r="E1933" s="14" t="n"/>
+      <c r="E1933" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、江浙菜、清淡、鲜美、儿童、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1934" ht="48" customHeight="1" s="10">
       <c r="B1934" s="15" t="inlineStr">
@@ -42414,7 +43014,11 @@
           <t>第1步：取出蟹黄和蟹肉，留蟹盖备用。；第2步：取一锅加水烧开，放入鸡头米煮15分钟捞出备用。；第3步：取一锅，加入猪油烧化，再加入葱末和姜末爆香。；第4步：加入蟹肉翻炒出香味后，加入南瓜泥，煮好的鸡头米和鸡汤，小火慢煮5分钟后大火收浓，盛出备用。；第5步：把炒好的蟹肉放入蟹盖中，撒上马苏里拉芝士，放在烤盘上。；第6步：打开蒸烤一体机，将烤盘放在蒸烤一体机第 2层，开启电源，选择”开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1935" s="14" t="n"/>
+      <c r="E1935" s="14" t="inlineStr">
+        <is>
+          <t>晚餐、江浙菜、咸、甜、鲜美、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1936" ht="48" customHeight="1" s="10">
       <c r="B1936" s="15" t="inlineStr">
@@ -42610,7 +43214,7 @@
       </c>
       <c r="E1944" s="16" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、东北菜、辣、香辣、咸、上班族、烤制类</t>
         </is>
       </c>
     </row>
@@ -43249,7 +43853,7 @@
       </c>
       <c r="E1973" s="14" t="inlineStr">
         <is>
-          <t>烤制类</t>
+          <t>晚餐、地方风味、清淡、咸、便秘、烤制类</t>
         </is>
       </c>
     </row>
@@ -43313,7 +43917,11 @@
           <t>第1步：鲜虾吐司无需解冻，取出鲜虾吐司，放在铺有锡箔纸的蒸烤盘上；第2步：打开方太智能烹饪设备，将蒸烤盘放入设备中间层，开启电源，选择“开始烹饪”按键，按屏幕提示操作。</t>
         </is>
       </c>
-      <c r="E1976" s="16" t="n"/>
+      <c r="E1976" s="16" t="inlineStr">
+        <is>
+          <t>早餐、下午茶、西餐风味、咸、脆、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1977" ht="48" customHeight="1" s="10">
       <c r="B1977" s="13" t="inlineStr">
@@ -43419,7 +44027,11 @@
           <t>第1步：菜心去除老根，粗的茎对半切开。切成5厘米的段。；第2步：将蒜片和盐1g，白糖2g，鸡精0.5g，生抽10g，蚝油3g放入碗中拌匀，备用。；第3步：中号盘中加入猪油10g和玉米油10g。；第4步：中号盘放在蒸烤架上，放入机器第二层，开启电源，选择“ 开始烹饪”按键，按屏幕提示操作。；第5步：将蒜片和调味汁加入到菜心中，翻拌均匀备用。；第6步：热炒11min后后将菜心放入中号盘中拌匀。；第7步：关门继续烹饪。</t>
         </is>
       </c>
-      <c r="E1981" s="14" t="n"/>
+      <c r="E1981" s="14" t="inlineStr">
+        <is>
+          <t>午餐、晚餐、粤菜、清淡、蒜香、减脂、便秘、家常菜</t>
+        </is>
+      </c>
     </row>
     <row r="1982" ht="48" customHeight="1" s="10">
       <c r="B1982" s="15" t="inlineStr">
@@ -43613,7 +44225,11 @@
           <t>第1步：锅中加入100g大米和1000g水，盖上锅盖，先设置：8分钟/9档；再设置：45分钟/2档。；第2步：加入10只对虾、20个蛤蜊、20g花生酱、1小勺白胡椒粉和2小勺盐，搅拌均匀，盖上锅盖，设置：5分钟/5档。</t>
         </is>
       </c>
-      <c r="E1990" s="16" t="n"/>
+      <c r="E1990" s="16" t="inlineStr">
+        <is>
+          <t>早餐、晚餐、粤菜、清淡、鲜美、养胃、老人、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="1991" ht="48" customHeight="1" s="10">
       <c r="B1991" s="13" t="inlineStr">
@@ -43873,7 +44489,11 @@
           <t>第1步：主锅中加入高筋面粉、牛奶、鸡蛋、细砂糖、酵母和盐，盖上锅盖和量杯，设置：6分钟/揉面。；第2步：加入软化黄油，盖上锅盖和量杯，设置：8分钟/揉面。烹饪结束，将面团取出，折叠至表面光滑，放入料理盆中，盖上保鲜膜发酵至两倍大。</t>
         </is>
       </c>
-      <c r="E2002" s="16" t="n"/>
+      <c r="E2002" s="16" t="inlineStr">
+        <is>
+          <t>早餐、下午茶、西餐风味、甜、咸、儿童</t>
+        </is>
+      </c>
     </row>
     <row r="2003" ht="48" customHeight="1" s="10">
       <c r="B2003" s="13" t="inlineStr">
@@ -43929,7 +44549,14 @@
     <row r="2007">
       <c r="B2007" s="9" t="inlineStr">
         <is>
-          <t>已追加标签：烤制类 203 道、耗时长 118 道、汤类 111 道、家常菜 483 道（明细见仓库根目录 家常菜标签清单.md）</t>
+          <t>已追加标签：烤制类 206 道、耗时长 118 道、汤类 111 道、家常菜 529 道（明细见仓库根目录 家常菜标签清单.md）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="B2008" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 补全：211 道原无标签菜谱已人工逐条判标（明细见 补标清单.md）</t>
         </is>
       </c>
     </row>
